--- a/case_tshirts/Кейс 1_Бюджет проекта_ЗАПОЛНЕНО.xlsx
+++ b/case_tshirts/Кейс 1_Бюджет проекта_ЗАПОЛНЕНО.xlsx
@@ -532,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -921,10 +921,10 @@
     <xf numFmtId="165" fontId="21" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="21" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="1" fontId="21" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="21" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -940,11 +940,10 @@
     <xf numFmtId="166" fontId="0" fillId="16" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="22" fillId="16" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -2129,103 +2128,103 @@
     <row r="10" ht="15" customHeight="1" s="92">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>ИНВЕСТИЦИИ</t>
+          <t>ИНВЕСТИЦИИ (транши по потребности)</t>
         </is>
       </c>
       <c r="B10" s="105">
-        <f>IF(B$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(B$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(Параметры!$B$68,ROUNDUP((0-(Параметры!$B$76+(B3+B6+B9)-(B17+B22+B26+B34+B38+B42)-B43))/Параметры!$B$69,0)*Параметры!$B$69),Параметры!$B$73)</f>
         <v/>
       </c>
       <c r="C10" s="106">
-        <f>IF(C$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(C$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(B46+(C3+C6+C9)-(C17+C22+C26+C34+C38+C42)-C43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-B59))</f>
         <v/>
       </c>
       <c r="D10" s="106">
-        <f>IF(D$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(D$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(C46+(D3+D6+D9)-(D17+D22+D26+D34+D38+D42)-D43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-C59))</f>
         <v/>
       </c>
       <c r="E10" s="106">
-        <f>IF(E$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(E$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(D46+(E3+E6+E9)-(E17+E22+E26+E34+E38+E42)-E43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-D59))</f>
         <v/>
       </c>
       <c r="F10" s="106">
-        <f>IF(F$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(F$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(E46+(F3+F6+F9)-(F17+F22+F26+F34+F38+F42)-F43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-E59))</f>
         <v/>
       </c>
       <c r="G10" s="106">
-        <f>IF(G$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(G$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(F46+(G3+G6+G9)-(G17+G22+G26+G34+G38+G42)-G43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-F59))</f>
         <v/>
       </c>
       <c r="H10" s="106">
-        <f>IF(H$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(H$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(G46+(H3+H6+H9)-(H17+H22+H26+H34+H38+H42)-H43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-G59))</f>
         <v/>
       </c>
       <c r="I10" s="106">
-        <f>IF(I$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(I$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(H46+(I3+I6+I9)-(I17+I22+I26+I34+I38+I42)-I43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-H59))</f>
         <v/>
       </c>
       <c r="J10" s="106">
-        <f>IF(J$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(J$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(I46+(J3+J6+J9)-(J17+J22+J26+J34+J38+J42)-J43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-I59))</f>
         <v/>
       </c>
       <c r="K10" s="106">
-        <f>IF(K$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(K$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(J46+(K3+K6+K9)-(K17+K22+K26+K34+K38+K42)-K43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-J59))</f>
         <v/>
       </c>
       <c r="L10" s="106">
-        <f>IF(L$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(L$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(K46+(L3+L6+L9)-(L17+L22+L26+L34+L38+L42)-L43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-K59))</f>
         <v/>
       </c>
       <c r="M10" s="106">
-        <f>IF(M$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(M$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(L46+(M3+M6+M9)-(M17+M22+M26+M34+M38+M42)-M43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-L59))</f>
         <v/>
       </c>
       <c r="N10" s="106">
-        <f>IF(N$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(N$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(M46+(N3+N6+N9)-(N17+N22+N26+N34+N38+N42)-N43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-M59))</f>
         <v/>
       </c>
       <c r="O10" s="106">
-        <f>IF(O$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(O$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(N46+(O3+O6+O9)-(O17+O22+O26+O34+O38+O42)-O43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-N59))</f>
         <v/>
       </c>
       <c r="P10" s="106">
-        <f>IF(P$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(P$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(O46+(P3+P6+P9)-(P17+P22+P26+P34+P38+P42)-P43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-O59))</f>
         <v/>
       </c>
       <c r="Q10" s="106">
-        <f>IF(Q$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(Q$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(P46+(Q3+Q6+Q9)-(Q17+Q22+Q26+Q34+Q38+Q42)-Q43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-P59))</f>
         <v/>
       </c>
       <c r="R10" s="106">
-        <f>IF(R$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(R$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(Q46+(R3+R6+R9)-(R17+R22+R26+R34+R38+R42)-R43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-Q59))</f>
         <v/>
       </c>
       <c r="S10" s="106">
-        <f>IF(S$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(S$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(R46+(S3+S6+S9)-(S17+S22+S26+S34+S38+S42)-S43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-R59))</f>
         <v/>
       </c>
       <c r="T10" s="106">
-        <f>IF(T$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(T$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(S46+(T3+T6+T9)-(T17+T22+T26+T34+T38+T42)-T43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-S59))</f>
         <v/>
       </c>
       <c r="U10" s="106">
-        <f>IF(U$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(U$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(T46+(U3+U6+U9)-(U17+U22+U26+U34+U38+U42)-U43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-T59))</f>
         <v/>
       </c>
       <c r="V10" s="106">
-        <f>IF(V$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(V$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(U46+(V3+V6+V9)-(V17+V22+V26+V34+V38+V42)-V43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-U59))</f>
         <v/>
       </c>
       <c r="W10" s="106">
-        <f>IF(W$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(W$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(V46+(W3+W6+W9)-(W17+W22+W26+W34+W38+W42)-W43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-V59))</f>
         <v/>
       </c>
       <c r="X10" s="106">
-        <f>IF(X$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(X$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(W46+(X3+X6+X9)-(X17+X22+X26+X34+X38+X42)-X43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-W59))</f>
         <v/>
       </c>
       <c r="Y10" s="107">
-        <f>IF(Y$48=1,ROUNDUP($B$62*Параметры!$B$63/100000,0)*100000,IF(Y$48=Параметры!$B$64,ROUNDUP($B$62*(1-Параметры!$B$63)/100000,0)*100000,0))</f>
+        <f>MIN(MAX(0,ROUNDUP((Параметры!$B$70-(X46+(Y3+Y6+Y9)-(Y17+Y22+Y26+Y34+Y38+Y42)-Y43))/Параметры!$B$69,0)*Параметры!$B$69),MAX(0,Параметры!$B$73-X59))</f>
         <v/>
       </c>
       <c r="Z10" s="108">
@@ -2388,99 +2387,99 @@
         </is>
       </c>
       <c r="B13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(B$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(B$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(B$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="C13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(C$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(C$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(C$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="D13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(D$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(D$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(D$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="E13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(E$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(E$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(E$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="F13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(F$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(F$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(F$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="G13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(G$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(G$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(G$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="H13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(H$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(H$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(H$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="I13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(I$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(I$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(I$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="J13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(J$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(J$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(J$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="K13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(K$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(K$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(K$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="L13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(L$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(L$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(L$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="M13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(M$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(M$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(M$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="N13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(N$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(N$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(N$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="O13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(O$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(O$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(O$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="P13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(P$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(P$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(P$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Q13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(Q$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(Q$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(Q$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="R13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(R$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(R$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(R$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="S13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(S$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(S$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(S$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="T13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(T$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(T$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(T$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="U13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(U$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(U$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(U$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="V13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(V$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(V$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(V$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="W13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(W$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(W$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(W$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="X13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(X$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(X$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(X$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Y13" s="109">
-        <f>ROUND(Параметры!$B$32*IF(Y$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(Y$48&lt;Параметры!$B$35,0,ROUND(Параметры!$B$34*IF(Y$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Z13" s="110">
@@ -2497,99 +2496,99 @@
         </is>
       </c>
       <c r="B14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(B$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(B$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(B$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="C14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(C$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(C$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(C$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="D14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(D$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(D$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(D$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="E14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(E$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(E$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(E$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="F14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(F$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(F$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(F$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="G14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(G$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(G$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(G$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="H14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(H$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(H$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(H$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="I14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(I$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(I$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(I$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="J14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(J$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(J$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(J$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="K14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(K$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(K$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(K$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="L14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(L$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(L$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(L$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="M14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(M$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(M$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(M$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="N14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(N$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(N$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(N$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="O14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(O$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(O$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(O$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="P14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(P$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(P$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(P$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Q14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(Q$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(Q$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(Q$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="R14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(R$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(R$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(R$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="S14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(S$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(S$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(S$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="T14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(T$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(T$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(T$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="U14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(U$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(U$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(U$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="V14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(V$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(V$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(V$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="W14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(W$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(W$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(W$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="X14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(X$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(X$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(X$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Y14" s="109">
-        <f>ROUND(Параметры!$B$33*IF(Y$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(Y$48&lt;Параметры!$B$27,0,ROUND(Параметры!$B$26*IF(Y$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Z14" s="110">
@@ -2606,99 +2605,99 @@
         </is>
       </c>
       <c r="B15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="C15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="D15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="E15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="F15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="G15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="H15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="I15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="J15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="K15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="L15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="M15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="N15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="O15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="P15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="Q15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="R15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="S15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="T15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="U15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="V15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="W15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="X15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="Y15" s="109">
-        <f>Параметры!$B$46</f>
+        <f>Параметры!$B$51</f>
         <v/>
       </c>
       <c r="Z15" s="110">
@@ -2715,99 +2714,99 @@
         </is>
       </c>
       <c r="B16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="C16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="D16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="E16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="F16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="G16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="H16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="I16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="J16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="K16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="L16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="M16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="N16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="O16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="P16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="Q16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="R16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="S16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="T16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="U16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="V16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="W16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="X16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="Y16" s="109">
-        <f>Параметры!$B$47</f>
+        <f>Параметры!$B$52</f>
         <v/>
       </c>
       <c r="Z16" s="110">
@@ -2933,99 +2932,99 @@
         </is>
       </c>
       <c r="B18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="C18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="D18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="E18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="F18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="G18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="H18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="I18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="J18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="K18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="L18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="M18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="N18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="O18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="P18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="Q18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="R18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="S18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="T18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="U18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="V18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="W18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="X18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="Y18" s="111">
-        <f>Параметры!$B$48</f>
+        <f>Параметры!$B$53</f>
         <v/>
       </c>
       <c r="Z18" s="112">
@@ -3042,99 +3041,99 @@
         </is>
       </c>
       <c r="B19" s="111">
-        <f>ROUND((B34+B13+B14)*Параметры!$B$35,0)</f>
+        <f>ROUND((B34+B13+B14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="C19" s="111">
-        <f>ROUND((C34+C13+C14)*Параметры!$B$35,0)</f>
+        <f>ROUND((C34+C13+C14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="D19" s="111">
-        <f>ROUND((D34+D13+D14)*Параметры!$B$35,0)</f>
+        <f>ROUND((D34+D13+D14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="E19" s="111">
-        <f>ROUND((E34+E13+E14)*Параметры!$B$35,0)</f>
+        <f>ROUND((E34+E13+E14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="F19" s="111">
-        <f>ROUND((F34+F13+F14)*Параметры!$B$35,0)</f>
+        <f>ROUND((F34+F13+F14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="G19" s="111">
-        <f>ROUND((G34+G13+G14)*Параметры!$B$35,0)</f>
+        <f>ROUND((G34+G13+G14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="H19" s="111">
-        <f>ROUND((H34+H13+H14)*Параметры!$B$35,0)</f>
+        <f>ROUND((H34+H13+H14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="I19" s="111">
-        <f>ROUND((I34+I13+I14)*Параметры!$B$35,0)</f>
+        <f>ROUND((I34+I13+I14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="J19" s="111">
-        <f>ROUND((J34+J13+J14)*Параметры!$B$35,0)</f>
+        <f>ROUND((J34+J13+J14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="K19" s="111">
-        <f>ROUND((K34+K13+K14)*Параметры!$B$35,0)</f>
+        <f>ROUND((K34+K13+K14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="L19" s="111">
-        <f>ROUND((L34+L13+L14)*Параметры!$B$35,0)</f>
+        <f>ROUND((L34+L13+L14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="M19" s="111">
-        <f>ROUND((M34+M13+M14)*Параметры!$B$35,0)</f>
+        <f>ROUND((M34+M13+M14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="N19" s="111">
-        <f>ROUND((N34+N13+N14)*Параметры!$B$35,0)</f>
+        <f>ROUND((N34+N13+N14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="O19" s="111">
-        <f>ROUND((O34+O13+O14)*Параметры!$B$35,0)</f>
+        <f>ROUND((O34+O13+O14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="P19" s="111">
-        <f>ROUND((P34+P13+P14)*Параметры!$B$35,0)</f>
+        <f>ROUND((P34+P13+P14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="Q19" s="111">
-        <f>ROUND((Q34+Q13+Q14)*Параметры!$B$35,0)</f>
+        <f>ROUND((Q34+Q13+Q14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="R19" s="111">
-        <f>ROUND((R34+R13+R14)*Параметры!$B$35,0)</f>
+        <f>ROUND((R34+R13+R14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="S19" s="111">
-        <f>ROUND((S34+S13+S14)*Параметры!$B$35,0)</f>
+        <f>ROUND((S34+S13+S14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="T19" s="111">
-        <f>ROUND((T34+T13+T14)*Параметры!$B$35,0)</f>
+        <f>ROUND((T34+T13+T14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="U19" s="111">
-        <f>ROUND((U34+U13+U14)*Параметры!$B$35,0)</f>
+        <f>ROUND((U34+U13+U14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="V19" s="111">
-        <f>ROUND((V34+V13+V14)*Параметры!$B$35,0)</f>
+        <f>ROUND((V34+V13+V14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="W19" s="111">
-        <f>ROUND((W34+W13+W14)*Параметры!$B$35,0)</f>
+        <f>ROUND((W34+W13+W14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="X19" s="111">
-        <f>ROUND((X34+X13+X14)*Параметры!$B$35,0)</f>
+        <f>ROUND((X34+X13+X14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="Y19" s="111">
-        <f>ROUND((Y34+Y13+Y14)*Параметры!$B$35,0)</f>
+        <f>ROUND((Y34+Y13+Y14)*Параметры!$B$40,0)</f>
         <v/>
       </c>
       <c r="Z19" s="112">
@@ -3151,99 +3150,99 @@
         </is>
       </c>
       <c r="B20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((B3+B6+B9)-(B17+B18+B19+B21+B26+B34+B38+B42)),Параметры!$B$59*(B3+B6+B9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((B3+B6+B9)-(B17+B18+B19+B21+B26+B34+B38+B42)),Параметры!$B$65*(B3+B6+B9)),0)</f>
         <v/>
       </c>
       <c r="C20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((C3+C6+C9)-(C17+C18+C19+C21+C26+C34+C38+C42)),Параметры!$B$59*(C3+C6+C9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((C3+C6+C9)-(C17+C18+C19+C21+C26+C34+C38+C42)),Параметры!$B$65*(C3+C6+C9)),0)</f>
         <v/>
       </c>
       <c r="D20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((D3+D6+D9)-(D17+D18+D19+D21+D26+D34+D38+D42)),Параметры!$B$59*(D3+D6+D9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((D3+D6+D9)-(D17+D18+D19+D21+D26+D34+D38+D42)),Параметры!$B$65*(D3+D6+D9)),0)</f>
         <v/>
       </c>
       <c r="E20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((E3+E6+E9)-(E17+E18+E19+E21+E26+E34+E38+E42)),Параметры!$B$59*(E3+E6+E9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((E3+E6+E9)-(E17+E18+E19+E21+E26+E34+E38+E42)),Параметры!$B$65*(E3+E6+E9)),0)</f>
         <v/>
       </c>
       <c r="F20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((F3+F6+F9)-(F17+F18+F19+F21+F26+F34+F38+F42)),Параметры!$B$59*(F3+F6+F9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((F3+F6+F9)-(F17+F18+F19+F21+F26+F34+F38+F42)),Параметры!$B$65*(F3+F6+F9)),0)</f>
         <v/>
       </c>
       <c r="G20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((G3+G6+G9)-(G17+G18+G19+G21+G26+G34+G38+G42)),Параметры!$B$59*(G3+G6+G9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((G3+G6+G9)-(G17+G18+G19+G21+G26+G34+G38+G42)),Параметры!$B$65*(G3+G6+G9)),0)</f>
         <v/>
       </c>
       <c r="H20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((H3+H6+H9)-(H17+H18+H19+H21+H26+H34+H38+H42)),Параметры!$B$59*(H3+H6+H9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((H3+H6+H9)-(H17+H18+H19+H21+H26+H34+H38+H42)),Параметры!$B$65*(H3+H6+H9)),0)</f>
         <v/>
       </c>
       <c r="I20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((I3+I6+I9)-(I17+I18+I19+I21+I26+I34+I38+I42)),Параметры!$B$59*(I3+I6+I9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((I3+I6+I9)-(I17+I18+I19+I21+I26+I34+I38+I42)),Параметры!$B$65*(I3+I6+I9)),0)</f>
         <v/>
       </c>
       <c r="J20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((J3+J6+J9)-(J17+J18+J19+J21+J26+J34+J38+J42)),Параметры!$B$59*(J3+J6+J9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((J3+J6+J9)-(J17+J18+J19+J21+J26+J34+J38+J42)),Параметры!$B$65*(J3+J6+J9)),0)</f>
         <v/>
       </c>
       <c r="K20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((K3+K6+K9)-(K17+K18+K19+K21+K26+K34+K38+K42)),Параметры!$B$59*(K3+K6+K9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((K3+K6+K9)-(K17+K18+K19+K21+K26+K34+K38+K42)),Параметры!$B$65*(K3+K6+K9)),0)</f>
         <v/>
       </c>
       <c r="L20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((L3+L6+L9)-(L17+L18+L19+L21+L26+L34+L38+L42)),Параметры!$B$59*(L3+L6+L9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((L3+L6+L9)-(L17+L18+L19+L21+L26+L34+L38+L42)),Параметры!$B$65*(L3+L6+L9)),0)</f>
         <v/>
       </c>
       <c r="M20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((M3+M6+M9)-(M17+M18+M19+M21+M26+M34+M38+M42)),Параметры!$B$59*(M3+M6+M9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((M3+M6+M9)-(M17+M18+M19+M21+M26+M34+M38+M42)),Параметры!$B$65*(M3+M6+M9)),0)</f>
         <v/>
       </c>
       <c r="N20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((N3+N6+N9)-(N17+N18+N19+N21+N26+N34+N38+N42)),Параметры!$B$59*(N3+N6+N9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((N3+N6+N9)-(N17+N18+N19+N21+N26+N34+N38+N42)),Параметры!$B$65*(N3+N6+N9)),0)</f>
         <v/>
       </c>
       <c r="O20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((O3+O6+O9)-(O17+O18+O19+O21+O26+O34+O38+O42)),Параметры!$B$59*(O3+O6+O9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((O3+O6+O9)-(O17+O18+O19+O21+O26+O34+O38+O42)),Параметры!$B$65*(O3+O6+O9)),0)</f>
         <v/>
       </c>
       <c r="P20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((P3+P6+P9)-(P17+P18+P19+P21+P26+P34+P38+P42)),Параметры!$B$59*(P3+P6+P9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((P3+P6+P9)-(P17+P18+P19+P21+P26+P34+P38+P42)),Параметры!$B$65*(P3+P6+P9)),0)</f>
         <v/>
       </c>
       <c r="Q20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((Q3+Q6+Q9)-(Q17+Q18+Q19+Q21+Q26+Q34+Q38+Q42)),Параметры!$B$59*(Q3+Q6+Q9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((Q3+Q6+Q9)-(Q17+Q18+Q19+Q21+Q26+Q34+Q38+Q42)),Параметры!$B$65*(Q3+Q6+Q9)),0)</f>
         <v/>
       </c>
       <c r="R20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((R3+R6+R9)-(R17+R18+R19+R21+R26+R34+R38+R42)),Параметры!$B$59*(R3+R6+R9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((R3+R6+R9)-(R17+R18+R19+R21+R26+R34+R38+R42)),Параметры!$B$65*(R3+R6+R9)),0)</f>
         <v/>
       </c>
       <c r="S20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((S3+S6+S9)-(S17+S18+S19+S21+S26+S34+S38+S42)),Параметры!$B$59*(S3+S6+S9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((S3+S6+S9)-(S17+S18+S19+S21+S26+S34+S38+S42)),Параметры!$B$65*(S3+S6+S9)),0)</f>
         <v/>
       </c>
       <c r="T20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((T3+T6+T9)-(T17+T18+T19+T21+T26+T34+T38+T42)),Параметры!$B$59*(T3+T6+T9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((T3+T6+T9)-(T17+T18+T19+T21+T26+T34+T38+T42)),Параметры!$B$65*(T3+T6+T9)),0)</f>
         <v/>
       </c>
       <c r="U20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((U3+U6+U9)-(U17+U18+U19+U21+U26+U34+U38+U42)),Параметры!$B$59*(U3+U6+U9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((U3+U6+U9)-(U17+U18+U19+U21+U26+U34+U38+U42)),Параметры!$B$65*(U3+U6+U9)),0)</f>
         <v/>
       </c>
       <c r="V20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((V3+V6+V9)-(V17+V18+V19+V21+V26+V34+V38+V42)),Параметры!$B$59*(V3+V6+V9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((V3+V6+V9)-(V17+V18+V19+V21+V26+V34+V38+V42)),Параметры!$B$65*(V3+V6+V9)),0)</f>
         <v/>
       </c>
       <c r="W20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((W3+W6+W9)-(W17+W18+W19+W21+W26+W34+W38+W42)),Параметры!$B$59*(W3+W6+W9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((W3+W6+W9)-(W17+W18+W19+W21+W26+W34+W38+W42)),Параметры!$B$65*(W3+W6+W9)),0)</f>
         <v/>
       </c>
       <c r="X20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((X3+X6+X9)-(X17+X18+X19+X21+X26+X34+X38+X42)),Параметры!$B$59*(X3+X6+X9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((X3+X6+X9)-(X17+X18+X19+X21+X26+X34+X38+X42)),Параметры!$B$65*(X3+X6+X9)),0)</f>
         <v/>
       </c>
       <c r="Y20" s="111">
-        <f>ROUND(MAX(Параметры!$B$58*((Y3+Y6+Y9)-(Y17+Y18+Y19+Y21+Y26+Y34+Y38+Y42)),Параметры!$B$59*(Y3+Y6+Y9)),0)</f>
+        <f>ROUND(MAX(Параметры!$B$64*((Y3+Y6+Y9)-(Y17+Y18+Y19+Y21+Y26+Y34+Y38+Y42)),Параметры!$B$65*(Y3+Y6+Y9)),0)</f>
         <v/>
       </c>
       <c r="Z20" s="112">
@@ -3260,99 +3259,99 @@
         </is>
       </c>
       <c r="B21" s="111">
-        <f>ROUND((B3+B6)*Параметры!$B$49,0)</f>
+        <f>ROUND((B3+B6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="C21" s="111">
-        <f>ROUND((C3+C6)*Параметры!$B$49,0)</f>
+        <f>ROUND((C3+C6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="D21" s="111">
-        <f>ROUND((D3+D6)*Параметры!$B$49,0)</f>
+        <f>ROUND((D3+D6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="E21" s="111">
-        <f>ROUND((E3+E6)*Параметры!$B$49,0)</f>
+        <f>ROUND((E3+E6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="F21" s="111">
-        <f>ROUND((F3+F6)*Параметры!$B$49,0)</f>
+        <f>ROUND((F3+F6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="G21" s="111">
-        <f>ROUND((G3+G6)*Параметры!$B$49,0)</f>
+        <f>ROUND((G3+G6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="H21" s="111">
-        <f>ROUND((H3+H6)*Параметры!$B$49,0)</f>
+        <f>ROUND((H3+H6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="I21" s="111">
-        <f>ROUND((I3+I6)*Параметры!$B$49,0)</f>
+        <f>ROUND((I3+I6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="J21" s="111">
-        <f>ROUND((J3+J6)*Параметры!$B$49,0)</f>
+        <f>ROUND((J3+J6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="K21" s="111">
-        <f>ROUND((K3+K6)*Параметры!$B$49,0)</f>
+        <f>ROUND((K3+K6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="L21" s="111">
-        <f>ROUND((L3+L6)*Параметры!$B$49,0)</f>
+        <f>ROUND((L3+L6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="M21" s="111">
-        <f>ROUND((M3+M6)*Параметры!$B$49,0)</f>
+        <f>ROUND((M3+M6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="N21" s="111">
-        <f>ROUND((N3+N6)*Параметры!$B$49,0)</f>
+        <f>ROUND((N3+N6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="O21" s="111">
-        <f>ROUND((O3+O6)*Параметры!$B$49,0)</f>
+        <f>ROUND((O3+O6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="P21" s="111">
-        <f>ROUND((P3+P6)*Параметры!$B$49,0)</f>
+        <f>ROUND((P3+P6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="Q21" s="111">
-        <f>ROUND((Q3+Q6)*Параметры!$B$49,0)</f>
+        <f>ROUND((Q3+Q6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="R21" s="111">
-        <f>ROUND((R3+R6)*Параметры!$B$49,0)</f>
+        <f>ROUND((R3+R6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="S21" s="111">
-        <f>ROUND((S3+S6)*Параметры!$B$49,0)</f>
+        <f>ROUND((S3+S6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="T21" s="111">
-        <f>ROUND((T3+T6)*Параметры!$B$49,0)</f>
+        <f>ROUND((T3+T6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="U21" s="111">
-        <f>ROUND((U3+U6)*Параметры!$B$49,0)</f>
+        <f>ROUND((U3+U6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="V21" s="111">
-        <f>ROUND((V3+V6)*Параметры!$B$49,0)</f>
+        <f>ROUND((V3+V6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="W21" s="111">
-        <f>ROUND((W3+W6)*Параметры!$B$49,0)</f>
+        <f>ROUND((W3+W6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="X21" s="111">
-        <f>ROUND((X3+X6)*Параметры!$B$49,0)</f>
+        <f>ROUND((X3+X6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="Y21" s="111">
-        <f>ROUND((Y3+Y6)*Параметры!$B$49,0)</f>
+        <f>ROUND((Y3+Y6)*Параметры!$B$54,0)</f>
         <v/>
       </c>
       <c r="Z21" s="112">
@@ -3478,99 +3477,99 @@
         </is>
       </c>
       <c r="B23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(B3+B6+B9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(B3+B6+B9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="C23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(C3+C6+C9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(C3+C6+C9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="D23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(D3+D6+D9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(D3+D6+D9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="E23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(E3+E6+E9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(E3+E6+E9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="F23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(F3+F6+F9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(F3+F6+F9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="G23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(G3+G6+G9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(G3+G6+G9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="H23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(H3+H6+H9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(H3+H6+H9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="I23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(I3+I6+I9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(I3+I6+I9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="J23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(J3+J6+J9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(J3+J6+J9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="K23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(K3+K6+K9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(K3+K6+K9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="L23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(L3+L6+L9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(L3+L6+L9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="M23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(M3+M6+M9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(M3+M6+M9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="N23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(N3+N6+N9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(N3+N6+N9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="O23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(O3+O6+O9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(O3+O6+O9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="P23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(P3+P6+P9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(P3+P6+P9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="Q23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(Q3+Q6+Q9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(Q3+Q6+Q9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="R23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(R3+R6+R9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(R3+R6+R9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="S23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(S3+S6+S9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(S3+S6+S9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="T23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(T3+T6+T9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(T3+T6+T9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="U23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(U3+U6+U9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(U3+U6+U9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="V23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(V3+V6+V9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(V3+V6+V9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="W23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(W3+W6+W9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(W3+W6+W9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="X23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(X3+X6+X9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(X3+X6+X9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="Y23" s="113">
-        <f>ROUND(MAX(Параметры!$B$39,(Y3+Y6+Y9)*Параметры!$B$38),0)</f>
+        <f>ROUND(MAX(Параметры!$B$44,(Y3+Y6+Y9)*Параметры!$B$43),0)</f>
         <v/>
       </c>
       <c r="Z23" s="114">
@@ -3587,99 +3586,99 @@
         </is>
       </c>
       <c r="B24" s="113">
-        <f>IF(B$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(B$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="C24" s="113">
-        <f>IF(C$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(C$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="D24" s="113">
-        <f>IF(D$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(D$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="E24" s="113">
-        <f>IF(E$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(E$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="F24" s="113">
-        <f>IF(F$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(F$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="G24" s="113">
-        <f>IF(G$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(G$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="H24" s="113">
-        <f>IF(H$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(H$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="I24" s="113">
-        <f>IF(I$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(I$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="J24" s="113">
-        <f>IF(J$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(J$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="K24" s="113">
-        <f>IF(K$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(K$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="L24" s="113">
-        <f>IF(L$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(L$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="M24" s="113">
-        <f>IF(M$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(M$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="N24" s="113">
-        <f>IF(N$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(N$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="O24" s="113">
-        <f>IF(O$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(O$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="P24" s="113">
-        <f>IF(P$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(P$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="Q24" s="113">
-        <f>IF(Q$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(Q$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="R24" s="113">
-        <f>IF(R$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(R$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="S24" s="113">
-        <f>IF(S$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(S$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="T24" s="113">
-        <f>IF(T$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(T$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="U24" s="113">
-        <f>IF(U$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(U$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="V24" s="113">
-        <f>IF(V$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(V$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="W24" s="113">
-        <f>IF(W$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(W$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="X24" s="113">
-        <f>IF(X$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(X$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="Y24" s="113">
-        <f>IF(Y$48&lt;Параметры!$B$41,0,Параметры!$B$40)</f>
+        <f>IF(Y$48&lt;Параметры!$B$46,0,Параметры!$B$45)</f>
         <v/>
       </c>
       <c r="Z24" s="114">
@@ -3696,99 +3695,99 @@
         </is>
       </c>
       <c r="B25" s="113">
-        <f>IF(B$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(B$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="C25" s="113">
-        <f>IF(C$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(C$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="D25" s="113">
-        <f>IF(D$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(D$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="E25" s="113">
-        <f>IF(E$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(E$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="F25" s="113">
-        <f>IF(F$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(F$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="G25" s="113">
-        <f>IF(G$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(G$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="H25" s="113">
-        <f>IF(H$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(H$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="I25" s="113">
-        <f>IF(I$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(I$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="J25" s="113">
-        <f>IF(J$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(J$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="K25" s="113">
-        <f>IF(K$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(K$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="L25" s="113">
-        <f>IF(L$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(L$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="M25" s="113">
-        <f>IF(M$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(M$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="N25" s="113">
-        <f>IF(N$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(N$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="O25" s="113">
-        <f>IF(O$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(O$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="P25" s="113">
-        <f>IF(P$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(P$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="Q25" s="113">
-        <f>IF(Q$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(Q$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="R25" s="113">
-        <f>IF(R$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(R$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="S25" s="113">
-        <f>IF(S$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(S$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="T25" s="113">
-        <f>IF(T$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(T$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="U25" s="113">
-        <f>IF(U$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(U$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="V25" s="113">
-        <f>IF(V$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(V$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="W25" s="113">
-        <f>IF(W$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(W$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="X25" s="113">
-        <f>IF(X$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(X$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="Y25" s="113">
-        <f>IF(Y$48&lt;Параметры!$B$43,0,Параметры!$B$42)</f>
+        <f>IF(Y$48&lt;Параметры!$B$48,0,Параметры!$B$47)</f>
         <v/>
       </c>
       <c r="Z25" s="114">
@@ -3914,99 +3913,99 @@
         </is>
       </c>
       <c r="B27" s="115">
-        <f>ROUND((B3+B6+B9)*Параметры!$B$26,0)</f>
+        <f>IF(B$48&lt;Параметры!$B$30,0,ROUND((B3+B6+B9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="C27" s="115">
-        <f>ROUND((C3+C6+C9)*Параметры!$B$26,0)</f>
+        <f>IF(C$48&lt;Параметры!$B$30,0,ROUND((C3+C6+C9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="D27" s="115">
-        <f>ROUND((D3+D6+D9)*Параметры!$B$26,0)</f>
+        <f>IF(D$48&lt;Параметры!$B$30,0,ROUND((D3+D6+D9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="E27" s="115">
-        <f>ROUND((E3+E6+E9)*Параметры!$B$26,0)</f>
+        <f>IF(E$48&lt;Параметры!$B$30,0,ROUND((E3+E6+E9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="F27" s="115">
-        <f>ROUND((F3+F6+F9)*Параметры!$B$26,0)</f>
+        <f>IF(F$48&lt;Параметры!$B$30,0,ROUND((F3+F6+F9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="G27" s="115">
-        <f>ROUND((G3+G6+G9)*Параметры!$B$26,0)</f>
+        <f>IF(G$48&lt;Параметры!$B$30,0,ROUND((G3+G6+G9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="H27" s="115">
-        <f>ROUND((H3+H6+H9)*Параметры!$B$26,0)</f>
+        <f>IF(H$48&lt;Параметры!$B$30,0,ROUND((H3+H6+H9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="I27" s="115">
-        <f>ROUND((I3+I6+I9)*Параметры!$B$26,0)</f>
+        <f>IF(I$48&lt;Параметры!$B$30,0,ROUND((I3+I6+I9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="J27" s="115">
-        <f>ROUND((J3+J6+J9)*Параметры!$B$26,0)</f>
+        <f>IF(J$48&lt;Параметры!$B$30,0,ROUND((J3+J6+J9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="K27" s="115">
-        <f>ROUND((K3+K6+K9)*Параметры!$B$26,0)</f>
+        <f>IF(K$48&lt;Параметры!$B$30,0,ROUND((K3+K6+K9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="L27" s="115">
-        <f>ROUND((L3+L6+L9)*Параметры!$B$26,0)</f>
+        <f>IF(L$48&lt;Параметры!$B$30,0,ROUND((L3+L6+L9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="M27" s="115">
-        <f>ROUND((M3+M6+M9)*Параметры!$B$26,0)</f>
+        <f>IF(M$48&lt;Параметры!$B$30,0,ROUND((M3+M6+M9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="N27" s="115">
-        <f>ROUND((N3+N6+N9)*Параметры!$B$26,0)</f>
+        <f>IF(N$48&lt;Параметры!$B$30,0,ROUND((N3+N6+N9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="O27" s="115">
-        <f>ROUND((O3+O6+O9)*Параметры!$B$26,0)</f>
+        <f>IF(O$48&lt;Параметры!$B$30,0,ROUND((O3+O6+O9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="P27" s="115">
-        <f>ROUND((P3+P6+P9)*Параметры!$B$26,0)</f>
+        <f>IF(P$48&lt;Параметры!$B$30,0,ROUND((P3+P6+P9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="Q27" s="115">
-        <f>ROUND((Q3+Q6+Q9)*Параметры!$B$26,0)</f>
+        <f>IF(Q$48&lt;Параметры!$B$30,0,ROUND((Q3+Q6+Q9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="R27" s="115">
-        <f>ROUND((R3+R6+R9)*Параметры!$B$26,0)</f>
+        <f>IF(R$48&lt;Параметры!$B$30,0,ROUND((R3+R6+R9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="S27" s="115">
-        <f>ROUND((S3+S6+S9)*Параметры!$B$26,0)</f>
+        <f>IF(S$48&lt;Параметры!$B$30,0,ROUND((S3+S6+S9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="T27" s="115">
-        <f>ROUND((T3+T6+T9)*Параметры!$B$26,0)</f>
+        <f>IF(T$48&lt;Параметры!$B$30,0,ROUND((T3+T6+T9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="U27" s="115">
-        <f>ROUND((U3+U6+U9)*Параметры!$B$26,0)</f>
+        <f>IF(U$48&lt;Параметры!$B$30,0,ROUND((U3+U6+U9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="V27" s="115">
-        <f>ROUND((V3+V6+V9)*Параметры!$B$26,0)</f>
+        <f>IF(V$48&lt;Параметры!$B$30,0,ROUND((V3+V6+V9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="W27" s="115">
-        <f>ROUND((W3+W6+W9)*Параметры!$B$26,0)</f>
+        <f>IF(W$48&lt;Параметры!$B$30,0,ROUND((W3+W6+W9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="X27" s="115">
-        <f>ROUND((X3+X6+X9)*Параметры!$B$26,0)</f>
+        <f>IF(X$48&lt;Параметры!$B$30,0,ROUND((X3+X6+X9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="Y27" s="115">
-        <f>ROUND((Y3+Y6+Y9)*Параметры!$B$26,0)</f>
+        <f>IF(Y$48&lt;Параметры!$B$30,0,ROUND((Y3+Y6+Y9)*Параметры!$B$29,0))</f>
         <v/>
       </c>
       <c r="Z27" s="116">
@@ -4023,99 +4022,99 @@
         </is>
       </c>
       <c r="B28" s="115">
-        <f>IF(B$48&lt;Параметры!$B$29,0,ROUND((B3+B6+B9)*Параметры!$B$28,0))</f>
+        <f>IF(B$48&lt;Параметры!$B$38,0,ROUND((B3+B6+B9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="C28" s="115">
-        <f>IF(C$48&lt;Параметры!$B$29,0,ROUND((C3+C6+C9)*Параметры!$B$28,0))</f>
+        <f>IF(C$48&lt;Параметры!$B$38,0,ROUND((C3+C6+C9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="D28" s="115">
-        <f>IF(D$48&lt;Параметры!$B$29,0,ROUND((D3+D6+D9)*Параметры!$B$28,0))</f>
+        <f>IF(D$48&lt;Параметры!$B$38,0,ROUND((D3+D6+D9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="E28" s="115">
-        <f>IF(E$48&lt;Параметры!$B$29,0,ROUND((E3+E6+E9)*Параметры!$B$28,0))</f>
+        <f>IF(E$48&lt;Параметры!$B$38,0,ROUND((E3+E6+E9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="F28" s="115">
-        <f>IF(F$48&lt;Параметры!$B$29,0,ROUND((F3+F6+F9)*Параметры!$B$28,0))</f>
+        <f>IF(F$48&lt;Параметры!$B$38,0,ROUND((F3+F6+F9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="G28" s="115">
-        <f>IF(G$48&lt;Параметры!$B$29,0,ROUND((G3+G6+G9)*Параметры!$B$28,0))</f>
+        <f>IF(G$48&lt;Параметры!$B$38,0,ROUND((G3+G6+G9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="H28" s="115">
-        <f>IF(H$48&lt;Параметры!$B$29,0,ROUND((H3+H6+H9)*Параметры!$B$28,0))</f>
+        <f>IF(H$48&lt;Параметры!$B$38,0,ROUND((H3+H6+H9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="I28" s="115">
-        <f>IF(I$48&lt;Параметры!$B$29,0,ROUND((I3+I6+I9)*Параметры!$B$28,0))</f>
+        <f>IF(I$48&lt;Параметры!$B$38,0,ROUND((I3+I6+I9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="J28" s="115">
-        <f>IF(J$48&lt;Параметры!$B$29,0,ROUND((J3+J6+J9)*Параметры!$B$28,0))</f>
+        <f>IF(J$48&lt;Параметры!$B$38,0,ROUND((J3+J6+J9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="K28" s="115">
-        <f>IF(K$48&lt;Параметры!$B$29,0,ROUND((K3+K6+K9)*Параметры!$B$28,0))</f>
+        <f>IF(K$48&lt;Параметры!$B$38,0,ROUND((K3+K6+K9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="L28" s="115">
-        <f>IF(L$48&lt;Параметры!$B$29,0,ROUND((L3+L6+L9)*Параметры!$B$28,0))</f>
+        <f>IF(L$48&lt;Параметры!$B$38,0,ROUND((L3+L6+L9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="M28" s="115">
-        <f>IF(M$48&lt;Параметры!$B$29,0,ROUND((M3+M6+M9)*Параметры!$B$28,0))</f>
+        <f>IF(M$48&lt;Параметры!$B$38,0,ROUND((M3+M6+M9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="N28" s="115">
-        <f>IF(N$48&lt;Параметры!$B$29,0,ROUND((N3+N6+N9)*Параметры!$B$28,0))</f>
+        <f>IF(N$48&lt;Параметры!$B$38,0,ROUND((N3+N6+N9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="O28" s="115">
-        <f>IF(O$48&lt;Параметры!$B$29,0,ROUND((O3+O6+O9)*Параметры!$B$28,0))</f>
+        <f>IF(O$48&lt;Параметры!$B$38,0,ROUND((O3+O6+O9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="P28" s="115">
-        <f>IF(P$48&lt;Параметры!$B$29,0,ROUND((P3+P6+P9)*Параметры!$B$28,0))</f>
+        <f>IF(P$48&lt;Параметры!$B$38,0,ROUND((P3+P6+P9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="Q28" s="115">
-        <f>IF(Q$48&lt;Параметры!$B$29,0,ROUND((Q3+Q6+Q9)*Параметры!$B$28,0))</f>
+        <f>IF(Q$48&lt;Параметры!$B$38,0,ROUND((Q3+Q6+Q9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="R28" s="115">
-        <f>IF(R$48&lt;Параметры!$B$29,0,ROUND((R3+R6+R9)*Параметры!$B$28,0))</f>
+        <f>IF(R$48&lt;Параметры!$B$38,0,ROUND((R3+R6+R9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="S28" s="115">
-        <f>IF(S$48&lt;Параметры!$B$29,0,ROUND((S3+S6+S9)*Параметры!$B$28,0))</f>
+        <f>IF(S$48&lt;Параметры!$B$38,0,ROUND((S3+S6+S9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="T28" s="115">
-        <f>IF(T$48&lt;Параметры!$B$29,0,ROUND((T3+T6+T9)*Параметры!$B$28,0))</f>
+        <f>IF(T$48&lt;Параметры!$B$38,0,ROUND((T3+T6+T9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="U28" s="115">
-        <f>IF(U$48&lt;Параметры!$B$29,0,ROUND((U3+U6+U9)*Параметры!$B$28,0))</f>
+        <f>IF(U$48&lt;Параметры!$B$38,0,ROUND((U3+U6+U9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="V28" s="115">
-        <f>IF(V$48&lt;Параметры!$B$29,0,ROUND((V3+V6+V9)*Параметры!$B$28,0))</f>
+        <f>IF(V$48&lt;Параметры!$B$38,0,ROUND((V3+V6+V9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="W28" s="115">
-        <f>IF(W$48&lt;Параметры!$B$29,0,ROUND((W3+W6+W9)*Параметры!$B$28,0))</f>
+        <f>IF(W$48&lt;Параметры!$B$38,0,ROUND((W3+W6+W9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="X28" s="115">
-        <f>IF(X$48&lt;Параметры!$B$29,0,ROUND((X3+X6+X9)*Параметры!$B$28,0))</f>
+        <f>IF(X$48&lt;Параметры!$B$38,0,ROUND((X3+X6+X9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="Y28" s="115">
-        <f>IF(Y$48&lt;Параметры!$B$29,0,ROUND((Y3+Y6+Y9)*Параметры!$B$28,0))</f>
+        <f>IF(Y$48&lt;Параметры!$B$38,0,ROUND((Y3+Y6+Y9)*Параметры!$B$37,0))</f>
         <v/>
       </c>
       <c r="Z28" s="116">
@@ -4132,99 +4131,99 @@
         </is>
       </c>
       <c r="B29" s="115">
-        <f>ROUND((B3+B6+B9)*Параметры!$B$31,0)</f>
+        <f>IF(B$48&lt;Параметры!$B$33,0,ROUND((B3+B6+B9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="C29" s="115">
-        <f>ROUND((C3+C6+C9)*Параметры!$B$31,0)</f>
+        <f>IF(C$48&lt;Параметры!$B$33,0,ROUND((C3+C6+C9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="D29" s="115">
-        <f>ROUND((D3+D6+D9)*Параметры!$B$31,0)</f>
+        <f>IF(D$48&lt;Параметры!$B$33,0,ROUND((D3+D6+D9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="E29" s="115">
-        <f>ROUND((E3+E6+E9)*Параметры!$B$31,0)</f>
+        <f>IF(E$48&lt;Параметры!$B$33,0,ROUND((E3+E6+E9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="F29" s="115">
-        <f>ROUND((F3+F6+F9)*Параметры!$B$31,0)</f>
+        <f>IF(F$48&lt;Параметры!$B$33,0,ROUND((F3+F6+F9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="G29" s="115">
-        <f>ROUND((G3+G6+G9)*Параметры!$B$31,0)</f>
+        <f>IF(G$48&lt;Параметры!$B$33,0,ROUND((G3+G6+G9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="H29" s="115">
-        <f>ROUND((H3+H6+H9)*Параметры!$B$31,0)</f>
+        <f>IF(H$48&lt;Параметры!$B$33,0,ROUND((H3+H6+H9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="I29" s="115">
-        <f>ROUND((I3+I6+I9)*Параметры!$B$31,0)</f>
+        <f>IF(I$48&lt;Параметры!$B$33,0,ROUND((I3+I6+I9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="J29" s="115">
-        <f>ROUND((J3+J6+J9)*Параметры!$B$31,0)</f>
+        <f>IF(J$48&lt;Параметры!$B$33,0,ROUND((J3+J6+J9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="K29" s="115">
-        <f>ROUND((K3+K6+K9)*Параметры!$B$31,0)</f>
+        <f>IF(K$48&lt;Параметры!$B$33,0,ROUND((K3+K6+K9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="L29" s="115">
-        <f>ROUND((L3+L6+L9)*Параметры!$B$31,0)</f>
+        <f>IF(L$48&lt;Параметры!$B$33,0,ROUND((L3+L6+L9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="M29" s="115">
-        <f>ROUND((M3+M6+M9)*Параметры!$B$31,0)</f>
+        <f>IF(M$48&lt;Параметры!$B$33,0,ROUND((M3+M6+M9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="N29" s="115">
-        <f>ROUND((N3+N6+N9)*Параметры!$B$31,0)</f>
+        <f>IF(N$48&lt;Параметры!$B$33,0,ROUND((N3+N6+N9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="O29" s="115">
-        <f>ROUND((O3+O6+O9)*Параметры!$B$31,0)</f>
+        <f>IF(O$48&lt;Параметры!$B$33,0,ROUND((O3+O6+O9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="P29" s="115">
-        <f>ROUND((P3+P6+P9)*Параметры!$B$31,0)</f>
+        <f>IF(P$48&lt;Параметры!$B$33,0,ROUND((P3+P6+P9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="Q29" s="115">
-        <f>ROUND((Q3+Q6+Q9)*Параметры!$B$31,0)</f>
+        <f>IF(Q$48&lt;Параметры!$B$33,0,ROUND((Q3+Q6+Q9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="R29" s="115">
-        <f>ROUND((R3+R6+R9)*Параметры!$B$31,0)</f>
+        <f>IF(R$48&lt;Параметры!$B$33,0,ROUND((R3+R6+R9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="S29" s="115">
-        <f>ROUND((S3+S6+S9)*Параметры!$B$31,0)</f>
+        <f>IF(S$48&lt;Параметры!$B$33,0,ROUND((S3+S6+S9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="T29" s="115">
-        <f>ROUND((T3+T6+T9)*Параметры!$B$31,0)</f>
+        <f>IF(T$48&lt;Параметры!$B$33,0,ROUND((T3+T6+T9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="U29" s="115">
-        <f>ROUND((U3+U6+U9)*Параметры!$B$31,0)</f>
+        <f>IF(U$48&lt;Параметры!$B$33,0,ROUND((U3+U6+U9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="V29" s="115">
-        <f>ROUND((V3+V6+V9)*Параметры!$B$31,0)</f>
+        <f>IF(V$48&lt;Параметры!$B$33,0,ROUND((V3+V6+V9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="W29" s="115">
-        <f>ROUND((W3+W6+W9)*Параметры!$B$31,0)</f>
+        <f>IF(W$48&lt;Параметры!$B$33,0,ROUND((W3+W6+W9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="X29" s="115">
-        <f>ROUND((X3+X6+X9)*Параметры!$B$31,0)</f>
+        <f>IF(X$48&lt;Параметры!$B$33,0,ROUND((X3+X6+X9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="Y29" s="115">
-        <f>ROUND((Y3+Y6+Y9)*Параметры!$B$31,0)</f>
+        <f>IF(Y$48&lt;Параметры!$B$33,0,ROUND((Y3+Y6+Y9)*Параметры!$B$32,0))</f>
         <v/>
       </c>
       <c r="Z29" s="116">
@@ -4241,99 +4240,99 @@
         </is>
       </c>
       <c r="B30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(B$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(B$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(B$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="C30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(C$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(C$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(C$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="D30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(D$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(D$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(D$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="E30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(E$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(E$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(E$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="F30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(F$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(F$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(F$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="G30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(G$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(G$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(G$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="H30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(H$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(H$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(H$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="I30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(I$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(I$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(I$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="J30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(J$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(J$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(J$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="K30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(K$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(K$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(K$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="L30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(L$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(L$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(L$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="M30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(M$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(M$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(M$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="N30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(N$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(N$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(N$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="O30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(O$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(O$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(O$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="P30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(P$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(P$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(P$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Q30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(Q$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(Q$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(Q$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="R30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(R$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(R$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(R$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="S30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(S$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(S$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(S$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="T30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(T$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(T$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(T$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="U30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(U$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(U$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(U$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="V30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(V$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(V$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(V$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="W30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(W$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(W$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(W$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="X30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(X$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(X$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(X$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Y30" s="115">
-        <f>ROUND(Параметры!$B$25*IF(Y$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(Y$48&lt;Параметры!$B$30,0,ROUND(Параметры!$B$28*IF(Y$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Z30" s="116">
@@ -4350,99 +4349,99 @@
         </is>
       </c>
       <c r="B31" s="115">
-        <f>IF(B$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(B$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(B$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(B$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="C31" s="115">
-        <f>IF(C$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(C$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(C$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(C$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="D31" s="115">
-        <f>IF(D$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(D$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(D$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(D$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="E31" s="115">
-        <f>IF(E$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(E$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(E$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(E$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="F31" s="115">
-        <f>IF(F$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(F$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(F$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(F$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="G31" s="115">
-        <f>IF(G$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(G$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(G$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(G$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="H31" s="115">
-        <f>IF(H$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(H$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(H$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(H$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="I31" s="115">
-        <f>IF(I$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(I$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(I$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(I$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="J31" s="115">
-        <f>IF(J$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(J$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(J$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(J$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="K31" s="115">
-        <f>IF(K$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(K$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(K$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(K$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="L31" s="115">
-        <f>IF(L$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(L$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(L$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(L$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="M31" s="115">
-        <f>IF(M$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(M$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(M$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(M$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="N31" s="115">
-        <f>IF(N$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(N$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(N$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(N$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="O31" s="115">
-        <f>IF(O$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(O$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(O$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(O$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="P31" s="115">
-        <f>IF(P$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(P$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(P$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(P$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Q31" s="115">
-        <f>IF(Q$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(Q$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(Q$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(Q$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="R31" s="115">
-        <f>IF(R$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(R$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(R$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(R$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="S31" s="115">
-        <f>IF(S$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(S$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(S$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(S$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="T31" s="115">
-        <f>IF(T$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(T$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(T$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(T$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="U31" s="115">
-        <f>IF(U$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(U$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(U$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(U$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="V31" s="115">
-        <f>IF(V$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(V$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(V$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(V$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="W31" s="115">
-        <f>IF(W$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(W$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(W$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(W$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="X31" s="115">
-        <f>IF(X$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(X$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(X$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(X$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Y31" s="115">
-        <f>IF(Y$48&lt;Параметры!$B$29,0,ROUND(Параметры!$B$27*IF(Y$48&lt;=12,1,1+Параметры!$B$34),0))</f>
+        <f>IF(Y$48&lt;Параметры!$B$38,0,ROUND(Параметры!$B$36*IF(Y$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Z31" s="116">
@@ -4459,99 +4458,99 @@
         </is>
       </c>
       <c r="B32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(B$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(B$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(B$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="C32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(C$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(C$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(C$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="D32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(D$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(D$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(D$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="E32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(E$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(E$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(E$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="F32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(F$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(F$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(F$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="G32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(G$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(G$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(G$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="H32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(H$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(H$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(H$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="I32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(I$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(I$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(I$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="J32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(J$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(J$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(J$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="K32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(K$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(K$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(K$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="L32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(L$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(L$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(L$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="M32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(M$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(M$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(M$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="N32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(N$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(N$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(N$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="O32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(O$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(O$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(O$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="P32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(P$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(P$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(P$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Q32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(Q$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(Q$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(Q$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="R32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(R$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(R$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(R$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="S32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(S$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(S$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(S$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="T32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(T$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(T$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(T$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="U32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(U$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(U$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(U$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="V32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(V$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(V$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(V$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="W32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(W$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(W$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(W$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="X32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(X$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(X$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(X$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Y32" s="115">
-        <f>ROUND(Параметры!$B$30*IF(Y$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(Y$48&lt;Параметры!$B$33,0,ROUND(Параметры!$B$31*IF(Y$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Z32" s="116">
@@ -4568,99 +4567,99 @@
         </is>
       </c>
       <c r="B33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(B$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(B$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(B$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="C33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(C$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(C$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(C$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="D33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(D$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(D$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(D$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="E33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(E$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(E$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(E$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="F33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(F$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(F$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(F$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="G33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(G$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(G$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(G$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="H33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(H$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(H$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(H$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="I33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(I$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(I$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(I$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="J33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(J$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(J$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(J$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="K33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(K$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(K$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(K$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="L33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(L$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(L$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(L$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="M33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(M$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(M$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(M$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="N33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(N$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(N$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(N$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="O33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(O$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(O$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(O$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="P33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(P$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(P$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(P$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Q33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(Q$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(Q$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(Q$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="R33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(R$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(R$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(R$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="S33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(S$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(S$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(S$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="T33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(T$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(T$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(T$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="U33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(U$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(U$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(U$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="V33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(V$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(V$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(V$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="W33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(W$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(W$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(W$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="X33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(X$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(X$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(X$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Y33" s="115">
-        <f>ROUND(Параметры!$B$24*IF(Y$48&lt;=12,1,1+Параметры!$B$34),0)</f>
+        <f>IF(Y$48&lt;Параметры!$B$25,0,ROUND(Параметры!$B$24*IF(Y$48&lt;=12,1,1+Параметры!$B$39),0))</f>
         <v/>
       </c>
       <c r="Z33" s="116">
@@ -4786,99 +4785,99 @@
         </is>
       </c>
       <c r="B35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(B$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="C35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(C$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="D35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(D$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="E35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(E$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="F35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(F$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="G35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(G$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="H35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(H$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="I35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(I$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="J35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(J$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="K35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(K$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="L35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(L$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="M35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(M$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="N35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(N$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="O35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(O$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="P35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(P$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="Q35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(Q$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="R35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(R$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="S35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(S$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="T35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(T$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="U35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(U$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="V35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(V$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="W35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(W$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="X35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(X$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="Y35" s="117">
-        <f>Параметры!$B$50</f>
+        <f>IF(Y$48&lt;Параметры!$B$56,0,Параметры!$B$55)</f>
         <v/>
       </c>
       <c r="Z35" s="118">
@@ -4895,99 +4894,99 @@
         </is>
       </c>
       <c r="B36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="C36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="D36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="E36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="F36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="G36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="H36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="I36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="J36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="K36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="L36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="M36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="N36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="O36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="P36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="Q36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="R36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="S36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="T36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="U36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="V36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="W36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="X36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="Y36" s="117">
-        <f>Параметры!$B$51</f>
+        <f>Параметры!$B$57</f>
         <v/>
       </c>
       <c r="Z36" s="118">
@@ -5004,99 +5003,99 @@
         </is>
       </c>
       <c r="B37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="C37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="D37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="E37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="F37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="G37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="H37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="I37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="J37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="K37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="L37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="M37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="N37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="O37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="P37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="Q37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="R37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="S37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="T37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="U37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="V37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="W37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="X37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="Y37" s="117">
-        <f>Параметры!$B$52</f>
+        <f>Параметры!$B$58</f>
         <v/>
       </c>
       <c r="Z37" s="118">
@@ -5222,7 +5221,7 @@
         </is>
       </c>
       <c r="B39" s="119">
-        <f>B50+IF(Параметры!$B$55=1,C50,0)</f>
+        <f>B50+IF(Параметры!$B$61=1,C50,0)</f>
         <v/>
       </c>
       <c r="C39" s="119">
@@ -5331,99 +5330,99 @@
         </is>
       </c>
       <c r="B40" s="119">
-        <f>ROUND((B3+B6+B9)*Параметры!$B$53,0)</f>
+        <f>ROUND((B3+B6+B9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="C40" s="119">
-        <f>ROUND((C3+C6+C9)*Параметры!$B$53,0)</f>
+        <f>ROUND((C3+C6+C9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="D40" s="119">
-        <f>ROUND((D3+D6+D9)*Параметры!$B$53,0)</f>
+        <f>ROUND((D3+D6+D9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="E40" s="119">
-        <f>ROUND((E3+E6+E9)*Параметры!$B$53,0)</f>
+        <f>ROUND((E3+E6+E9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="F40" s="119">
-        <f>ROUND((F3+F6+F9)*Параметры!$B$53,0)</f>
+        <f>ROUND((F3+F6+F9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="G40" s="119">
-        <f>ROUND((G3+G6+G9)*Параметры!$B$53,0)</f>
+        <f>ROUND((G3+G6+G9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="H40" s="119">
-        <f>ROUND((H3+H6+H9)*Параметры!$B$53,0)</f>
+        <f>ROUND((H3+H6+H9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="I40" s="119">
-        <f>ROUND((I3+I6+I9)*Параметры!$B$53,0)</f>
+        <f>ROUND((I3+I6+I9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="J40" s="119">
-        <f>ROUND((J3+J6+J9)*Параметры!$B$53,0)</f>
+        <f>ROUND((J3+J6+J9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="K40" s="119">
-        <f>ROUND((K3+K6+K9)*Параметры!$B$53,0)</f>
+        <f>ROUND((K3+K6+K9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="L40" s="119">
-        <f>ROUND((L3+L6+L9)*Параметры!$B$53,0)</f>
+        <f>ROUND((L3+L6+L9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="M40" s="119">
-        <f>ROUND((M3+M6+M9)*Параметры!$B$53,0)</f>
+        <f>ROUND((M3+M6+M9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="N40" s="119">
-        <f>ROUND((N3+N6+N9)*Параметры!$B$53,0)</f>
+        <f>ROUND((N3+N6+N9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="O40" s="119">
-        <f>ROUND((O3+O6+O9)*Параметры!$B$53,0)</f>
+        <f>ROUND((O3+O6+O9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="P40" s="119">
-        <f>ROUND((P3+P6+P9)*Параметры!$B$53,0)</f>
+        <f>ROUND((P3+P6+P9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="Q40" s="119">
-        <f>ROUND((Q3+Q6+Q9)*Параметры!$B$53,0)</f>
+        <f>ROUND((Q3+Q6+Q9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="R40" s="119">
-        <f>ROUND((R3+R6+R9)*Параметры!$B$53,0)</f>
+        <f>ROUND((R3+R6+R9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="S40" s="119">
-        <f>ROUND((S3+S6+S9)*Параметры!$B$53,0)</f>
+        <f>ROUND((S3+S6+S9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="T40" s="119">
-        <f>ROUND((T3+T6+T9)*Параметры!$B$53,0)</f>
+        <f>ROUND((T3+T6+T9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="U40" s="119">
-        <f>ROUND((U3+U6+U9)*Параметры!$B$53,0)</f>
+        <f>ROUND((U3+U6+U9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="V40" s="119">
-        <f>ROUND((V3+V6+V9)*Параметры!$B$53,0)</f>
+        <f>ROUND((V3+V6+V9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="W40" s="119">
-        <f>ROUND((W3+W6+W9)*Параметры!$B$53,0)</f>
+        <f>ROUND((W3+W6+W9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="X40" s="119">
-        <f>ROUND((X3+X6+X9)*Параметры!$B$53,0)</f>
+        <f>ROUND((X3+X6+X9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="Y40" s="119">
-        <f>ROUND((Y3+Y6+Y9)*Параметры!$B$53,0)</f>
+        <f>ROUND((Y3+Y6+Y9)*Параметры!$B$59,0)</f>
         <v/>
       </c>
       <c r="Z40" s="120">
@@ -5440,99 +5439,99 @@
         </is>
       </c>
       <c r="B41" s="119">
-        <f>ROUND((B3+B6)*Параметры!$B$54,0)</f>
+        <f>ROUND((B3+B6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="C41" s="119">
-        <f>ROUND((C3+C6)*Параметры!$B$54,0)</f>
+        <f>ROUND((C3+C6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="D41" s="119">
-        <f>ROUND((D3+D6)*Параметры!$B$54,0)</f>
+        <f>ROUND((D3+D6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="E41" s="119">
-        <f>ROUND((E3+E6)*Параметры!$B$54,0)</f>
+        <f>ROUND((E3+E6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="F41" s="119">
-        <f>ROUND((F3+F6)*Параметры!$B$54,0)</f>
+        <f>ROUND((F3+F6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="G41" s="119">
-        <f>ROUND((G3+G6)*Параметры!$B$54,0)</f>
+        <f>ROUND((G3+G6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="H41" s="119">
-        <f>ROUND((H3+H6)*Параметры!$B$54,0)</f>
+        <f>ROUND((H3+H6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="I41" s="119">
-        <f>ROUND((I3+I6)*Параметры!$B$54,0)</f>
+        <f>ROUND((I3+I6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="J41" s="119">
-        <f>ROUND((J3+J6)*Параметры!$B$54,0)</f>
+        <f>ROUND((J3+J6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="K41" s="119">
-        <f>ROUND((K3+K6)*Параметры!$B$54,0)</f>
+        <f>ROUND((K3+K6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="L41" s="119">
-        <f>ROUND((L3+L6)*Параметры!$B$54,0)</f>
+        <f>ROUND((L3+L6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="M41" s="119">
-        <f>ROUND((M3+M6)*Параметры!$B$54,0)</f>
+        <f>ROUND((M3+M6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="N41" s="119">
-        <f>ROUND((N3+N6)*Параметры!$B$54,0)</f>
+        <f>ROUND((N3+N6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="O41" s="119">
-        <f>ROUND((O3+O6)*Параметры!$B$54,0)</f>
+        <f>ROUND((O3+O6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="P41" s="119">
-        <f>ROUND((P3+P6)*Параметры!$B$54,0)</f>
+        <f>ROUND((P3+P6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="Q41" s="119">
-        <f>ROUND((Q3+Q6)*Параметры!$B$54,0)</f>
+        <f>ROUND((Q3+Q6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="R41" s="119">
-        <f>ROUND((R3+R6)*Параметры!$B$54,0)</f>
+        <f>ROUND((R3+R6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="S41" s="119">
-        <f>ROUND((S3+S6)*Параметры!$B$54,0)</f>
+        <f>ROUND((S3+S6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="T41" s="119">
-        <f>ROUND((T3+T6)*Параметры!$B$54,0)</f>
+        <f>ROUND((T3+T6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="U41" s="119">
-        <f>ROUND((U3+U6)*Параметры!$B$54,0)</f>
+        <f>ROUND((U3+U6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="V41" s="119">
-        <f>ROUND((V3+V6)*Параметры!$B$54,0)</f>
+        <f>ROUND((V3+V6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="W41" s="119">
-        <f>ROUND((W3+W6)*Параметры!$B$54,0)</f>
+        <f>ROUND((W3+W6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="X41" s="119">
-        <f>ROUND((X3+X6)*Параметры!$B$54,0)</f>
+        <f>ROUND((X3+X6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="Y41" s="119">
-        <f>ROUND((Y3+Y6)*Параметры!$B$54,0)</f>
+        <f>ROUND((Y3+Y6)*Параметры!$B$60,0)</f>
         <v/>
       </c>
       <c r="Z41" s="120">
@@ -5658,99 +5657,99 @@
         </is>
       </c>
       <c r="B43" s="121">
-        <f>MIN(B49,ROUND(MAX(0,B53)*Параметры!$B$66,0),MAX(0,Параметры!$B$70+B11-(B17+B22+B26+B34+B38+B42)-Параметры!$B$67))</f>
+        <f>MIN(B49,ROUND(MAX(0,B53)*Параметры!$B$72,0),MAX(0,Параметры!$B$76+(B3+B6+B9)-(B17+B22+B26+B34+B38+B42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="C43" s="121">
-        <f>MIN(C49,ROUND(MAX(0,C53)*Параметры!$B$66,0),MAX(0,B46+C11-(C17+C22+C26+C34+C38+C42)-Параметры!$B$67))</f>
+        <f>MIN(C49,ROUND(MAX(0,C53)*Параметры!$B$72,0),MAX(0,B46+(C3+C6+C9)-(C17+C22+C26+C34+C38+C42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="D43" s="121">
-        <f>MIN(D49,ROUND(MAX(0,D53)*Параметры!$B$66,0),MAX(0,C46+D11-(D17+D22+D26+D34+D38+D42)-Параметры!$B$67))</f>
+        <f>MIN(D49,ROUND(MAX(0,D53)*Параметры!$B$72,0),MAX(0,C46+(D3+D6+D9)-(D17+D22+D26+D34+D38+D42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="E43" s="121">
-        <f>MIN(E49,ROUND(MAX(0,E53)*Параметры!$B$66,0),MAX(0,D46+E11-(E17+E22+E26+E34+E38+E42)-Параметры!$B$67))</f>
+        <f>MIN(E49,ROUND(MAX(0,E53)*Параметры!$B$72,0),MAX(0,D46+(E3+E6+E9)-(E17+E22+E26+E34+E38+E42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="F43" s="121">
-        <f>MIN(F49,ROUND(MAX(0,F53)*Параметры!$B$66,0),MAX(0,E46+F11-(F17+F22+F26+F34+F38+F42)-Параметры!$B$67))</f>
+        <f>MIN(F49,ROUND(MAX(0,F53)*Параметры!$B$72,0),MAX(0,E46+(F3+F6+F9)-(F17+F22+F26+F34+F38+F42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="G43" s="121">
-        <f>MIN(G49,ROUND(MAX(0,G53)*Параметры!$B$66,0),MAX(0,F46+G11-(G17+G22+G26+G34+G38+G42)-Параметры!$B$67))</f>
+        <f>MIN(G49,ROUND(MAX(0,G53)*Параметры!$B$72,0),MAX(0,F46+(G3+G6+G9)-(G17+G22+G26+G34+G38+G42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="H43" s="121">
-        <f>MIN(H49,ROUND(MAX(0,H53)*Параметры!$B$66,0),MAX(0,G46+H11-(H17+H22+H26+H34+H38+H42)-Параметры!$B$67))</f>
+        <f>MIN(H49,ROUND(MAX(0,H53)*Параметры!$B$72,0),MAX(0,G46+(H3+H6+H9)-(H17+H22+H26+H34+H38+H42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="I43" s="121">
-        <f>MIN(I49,ROUND(MAX(0,I53)*Параметры!$B$66,0),MAX(0,H46+I11-(I17+I22+I26+I34+I38+I42)-Параметры!$B$67))</f>
+        <f>MIN(I49,ROUND(MAX(0,I53)*Параметры!$B$72,0),MAX(0,H46+(I3+I6+I9)-(I17+I22+I26+I34+I38+I42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="J43" s="121">
-        <f>MIN(J49,ROUND(MAX(0,J53)*Параметры!$B$66,0),MAX(0,I46+J11-(J17+J22+J26+J34+J38+J42)-Параметры!$B$67))</f>
+        <f>MIN(J49,ROUND(MAX(0,J53)*Параметры!$B$72,0),MAX(0,I46+(J3+J6+J9)-(J17+J22+J26+J34+J38+J42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="K43" s="121">
-        <f>MIN(K49,ROUND(MAX(0,K53)*Параметры!$B$66,0),MAX(0,J46+K11-(K17+K22+K26+K34+K38+K42)-Параметры!$B$67))</f>
+        <f>MIN(K49,ROUND(MAX(0,K53)*Параметры!$B$72,0),MAX(0,J46+(K3+K6+K9)-(K17+K22+K26+K34+K38+K42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="L43" s="121">
-        <f>MIN(L49,ROUND(MAX(0,L53)*Параметры!$B$66,0),MAX(0,K46+L11-(L17+L22+L26+L34+L38+L42)-Параметры!$B$67))</f>
+        <f>MIN(L49,ROUND(MAX(0,L53)*Параметры!$B$72,0),MAX(0,K46+(L3+L6+L9)-(L17+L22+L26+L34+L38+L42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="M43" s="121">
-        <f>MIN(M49,ROUND(MAX(0,M53)*Параметры!$B$66,0),MAX(0,L46+M11-(M17+M22+M26+M34+M38+M42)-Параметры!$B$67))</f>
+        <f>MIN(M49,ROUND(MAX(0,M53)*Параметры!$B$72,0),MAX(0,L46+(M3+M6+M9)-(M17+M22+M26+M34+M38+M42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="N43" s="121">
-        <f>MIN(N49,ROUND(MAX(0,N53)*Параметры!$B$66,0),MAX(0,M46+N11-(N17+N22+N26+N34+N38+N42)-Параметры!$B$67))</f>
+        <f>MIN(N49,ROUND(MAX(0,N53)*Параметры!$B$72,0),MAX(0,M46+(N3+N6+N9)-(N17+N22+N26+N34+N38+N42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="O43" s="121">
-        <f>MIN(O49,ROUND(MAX(0,O53)*Параметры!$B$66,0),MAX(0,N46+O11-(O17+O22+O26+O34+O38+O42)-Параметры!$B$67))</f>
+        <f>MIN(O49,ROUND(MAX(0,O53)*Параметры!$B$72,0),MAX(0,N46+(O3+O6+O9)-(O17+O22+O26+O34+O38+O42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="P43" s="121">
-        <f>MIN(P49,ROUND(MAX(0,P53)*Параметры!$B$66,0),MAX(0,O46+P11-(P17+P22+P26+P34+P38+P42)-Параметры!$B$67))</f>
+        <f>MIN(P49,ROUND(MAX(0,P53)*Параметры!$B$72,0),MAX(0,O46+(P3+P6+P9)-(P17+P22+P26+P34+P38+P42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="Q43" s="121">
-        <f>MIN(Q49,ROUND(MAX(0,Q53)*Параметры!$B$66,0),MAX(0,P46+Q11-(Q17+Q22+Q26+Q34+Q38+Q42)-Параметры!$B$67))</f>
+        <f>MIN(Q49,ROUND(MAX(0,Q53)*Параметры!$B$72,0),MAX(0,P46+(Q3+Q6+Q9)-(Q17+Q22+Q26+Q34+Q38+Q42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="R43" s="121">
-        <f>MIN(R49,ROUND(MAX(0,R53)*Параметры!$B$66,0),MAX(0,Q46+R11-(R17+R22+R26+R34+R38+R42)-Параметры!$B$67))</f>
+        <f>MIN(R49,ROUND(MAX(0,R53)*Параметры!$B$72,0),MAX(0,Q46+(R3+R6+R9)-(R17+R22+R26+R34+R38+R42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="S43" s="121">
-        <f>MIN(S49,ROUND(MAX(0,S53)*Параметры!$B$66,0),MAX(0,R46+S11-(S17+S22+S26+S34+S38+S42)-Параметры!$B$67))</f>
+        <f>MIN(S49,ROUND(MAX(0,S53)*Параметры!$B$72,0),MAX(0,R46+(S3+S6+S9)-(S17+S22+S26+S34+S38+S42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="T43" s="121">
-        <f>MIN(T49,ROUND(MAX(0,T53)*Параметры!$B$66,0),MAX(0,S46+T11-(T17+T22+T26+T34+T38+T42)-Параметры!$B$67))</f>
+        <f>MIN(T49,ROUND(MAX(0,T53)*Параметры!$B$72,0),MAX(0,S46+(T3+T6+T9)-(T17+T22+T26+T34+T38+T42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="U43" s="121">
-        <f>MIN(U49,ROUND(MAX(0,U53)*Параметры!$B$66,0),MAX(0,T46+U11-(U17+U22+U26+U34+U38+U42)-Параметры!$B$67))</f>
+        <f>MIN(U49,ROUND(MAX(0,U53)*Параметры!$B$72,0),MAX(0,T46+(U3+U6+U9)-(U17+U22+U26+U34+U38+U42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="V43" s="121">
-        <f>MIN(V49,ROUND(MAX(0,V53)*Параметры!$B$66,0),MAX(0,U46+V11-(V17+V22+V26+V34+V38+V42)-Параметры!$B$67))</f>
+        <f>MIN(V49,ROUND(MAX(0,V53)*Параметры!$B$72,0),MAX(0,U46+(V3+V6+V9)-(V17+V22+V26+V34+V38+V42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="W43" s="121">
-        <f>MIN(W49,ROUND(MAX(0,W53)*Параметры!$B$66,0),MAX(0,V46+W11-(W17+W22+W26+W34+W38+W42)-Параметры!$B$67))</f>
+        <f>MIN(W49,ROUND(MAX(0,W53)*Параметры!$B$72,0),MAX(0,V46+(W3+W6+W9)-(W17+W22+W26+W34+W38+W42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="X43" s="121">
-        <f>MIN(X49,ROUND(MAX(0,X53)*Параметры!$B$66,0),MAX(0,W46+X11-(X17+X22+X26+X34+X38+X42)-Параметры!$B$67))</f>
+        <f>MIN(X49,ROUND(MAX(0,X53)*Параметры!$B$72,0),MAX(0,W46+(X3+X6+X9)-(X17+X22+X26+X34+X38+X42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="Y43" s="121">
-        <f>MIN(Y49,ROUND(MAX(0,Y53)*Параметры!$B$66,0),MAX(0,X46+Y11-(Y17+Y22+Y26+Y34+Y38+Y42)-Параметры!$B$67))</f>
+        <f>MIN(Y49,ROUND(MAX(0,Y53)*Параметры!$B$72,0),MAX(0,X46+(Y3+Y6+Y9)-(Y17+Y22+Y26+Y34+Y38+Y42)-Параметры!$B$70))</f>
         <v/>
       </c>
       <c r="Z43" s="122">
@@ -5758,7 +5757,7 @@
         <v/>
       </c>
       <c r="AA43" s="78">
-        <f>ROUND($Z$10*Параметры!$B$65,0)-$Z$43</f>
+        <f>ROUND($Z$10*Параметры!$B$71,0)-$Z$43</f>
         <v/>
       </c>
       <c r="AB43" s="79" t="inlineStr">
@@ -6098,7 +6097,7 @@
         </is>
       </c>
       <c r="B47" s="123">
-        <f>Параметры!$B$70</f>
+        <f>Параметры!$B$76</f>
         <v/>
       </c>
       <c r="C47" s="6" t="n"/>
@@ -6237,103 +6236,103 @@
     <row r="49" ht="19.5" customHeight="1" s="92">
       <c r="A49" s="124" t="inlineStr">
         <is>
-          <t>Остаток обязательства перед инвестором (на начало мес.)</t>
+          <t>Обязательство перед инвестором на начало месяца</t>
         </is>
       </c>
       <c r="B49" s="126">
-        <f>ROUND(B10*Параметры!$B$65,0)</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="C49" s="126">
-        <f>B49-B43+ROUND(C10*Параметры!$B$65,0)</f>
+        <f>B49-B43+ROUND(B10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="D49" s="126">
-        <f>C49-C43+ROUND(D10*Параметры!$B$65,0)</f>
+        <f>C49-C43+ROUND(C10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="E49" s="126">
-        <f>D49-D43+ROUND(E10*Параметры!$B$65,0)</f>
+        <f>D49-D43+ROUND(D10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="F49" s="126">
-        <f>E49-E43+ROUND(F10*Параметры!$B$65,0)</f>
+        <f>E49-E43+ROUND(E10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="G49" s="126">
-        <f>F49-F43+ROUND(G10*Параметры!$B$65,0)</f>
+        <f>F49-F43+ROUND(F10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="H49" s="126">
-        <f>G49-G43+ROUND(H10*Параметры!$B$65,0)</f>
+        <f>G49-G43+ROUND(G10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="I49" s="126">
-        <f>H49-H43+ROUND(I10*Параметры!$B$65,0)</f>
+        <f>H49-H43+ROUND(H10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="J49" s="126">
-        <f>I49-I43+ROUND(J10*Параметры!$B$65,0)</f>
+        <f>I49-I43+ROUND(I10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="K49" s="126">
-        <f>J49-J43+ROUND(K10*Параметры!$B$65,0)</f>
+        <f>J49-J43+ROUND(J10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="L49" s="126">
-        <f>K49-K43+ROUND(L10*Параметры!$B$65,0)</f>
+        <f>K49-K43+ROUND(K10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="M49" s="126">
-        <f>L49-L43+ROUND(M10*Параметры!$B$65,0)</f>
+        <f>L49-L43+ROUND(L10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="N49" s="126">
-        <f>M49-M43+ROUND(N10*Параметры!$B$65,0)</f>
+        <f>M49-M43+ROUND(M10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="O49" s="126">
-        <f>N49-N43+ROUND(O10*Параметры!$B$65,0)</f>
+        <f>N49-N43+ROUND(N10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="P49" s="126">
-        <f>O49-O43+ROUND(P10*Параметры!$B$65,0)</f>
+        <f>O49-O43+ROUND(O10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="Q49" s="126">
-        <f>P49-P43+ROUND(Q10*Параметры!$B$65,0)</f>
+        <f>P49-P43+ROUND(P10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="R49" s="126">
-        <f>Q49-Q43+ROUND(R10*Параметры!$B$65,0)</f>
+        <f>Q49-Q43+ROUND(Q10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="S49" s="126">
-        <f>R49-R43+ROUND(S10*Параметры!$B$65,0)</f>
+        <f>R49-R43+ROUND(R10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="T49" s="126">
-        <f>S49-S43+ROUND(T10*Параметры!$B$65,0)</f>
+        <f>S49-S43+ROUND(S10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="U49" s="126">
-        <f>T49-T43+ROUND(U10*Параметры!$B$65,0)</f>
+        <f>T49-T43+ROUND(T10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="V49" s="126">
-        <f>U49-U43+ROUND(V10*Параметры!$B$65,0)</f>
+        <f>U49-U43+ROUND(U10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="W49" s="126">
-        <f>V49-V43+ROUND(W10*Параметры!$B$65,0)</f>
+        <f>V49-V43+ROUND(V10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="X49" s="126">
-        <f>W49-W43+ROUND(X10*Параметры!$B$65,0)</f>
+        <f>W49-W43+ROUND(W10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="Y49" s="126">
-        <f>X49-X43+ROUND(Y10*Параметры!$B$65,0)</f>
+        <f>X49-X43+ROUND(X10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="Z49" s="6" t="n"/>
@@ -7310,84 +7309,221 @@
       <c r="AB58" s="6" t="n"/>
     </row>
     <row r="59" ht="19.5" customHeight="1" s="92">
-      <c r="A59" s="6" t="n"/>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="6" t="n"/>
-      <c r="G59" s="6" t="n"/>
-      <c r="H59" s="6" t="n"/>
-      <c r="I59" s="6" t="n"/>
-      <c r="J59" s="6" t="n"/>
-      <c r="K59" s="6" t="n"/>
-      <c r="L59" s="6" t="n"/>
-      <c r="M59" s="6" t="n"/>
-      <c r="N59" s="6" t="n"/>
-      <c r="O59" s="6" t="n"/>
-      <c r="P59" s="6" t="n"/>
-      <c r="Q59" s="6" t="n"/>
-      <c r="R59" s="6" t="n"/>
-      <c r="S59" s="6" t="n"/>
-      <c r="T59" s="6" t="n"/>
-      <c r="U59" s="6" t="n"/>
-      <c r="V59" s="6" t="n"/>
-      <c r="W59" s="6" t="n"/>
-      <c r="X59" s="6" t="n"/>
-      <c r="Y59" s="6" t="n"/>
+      <c r="A59" s="124" t="inlineStr">
+        <is>
+          <t>Инвестиции накопленным итогом</t>
+        </is>
+      </c>
+      <c r="B59" s="126">
+        <f>B10</f>
+        <v/>
+      </c>
+      <c r="C59" s="126">
+        <f>B59+C10</f>
+        <v/>
+      </c>
+      <c r="D59" s="126">
+        <f>C59+D10</f>
+        <v/>
+      </c>
+      <c r="E59" s="126">
+        <f>D59+E10</f>
+        <v/>
+      </c>
+      <c r="F59" s="126">
+        <f>E59+F10</f>
+        <v/>
+      </c>
+      <c r="G59" s="126">
+        <f>F59+G10</f>
+        <v/>
+      </c>
+      <c r="H59" s="126">
+        <f>G59+H10</f>
+        <v/>
+      </c>
+      <c r="I59" s="126">
+        <f>H59+I10</f>
+        <v/>
+      </c>
+      <c r="J59" s="126">
+        <f>I59+J10</f>
+        <v/>
+      </c>
+      <c r="K59" s="126">
+        <f>J59+K10</f>
+        <v/>
+      </c>
+      <c r="L59" s="126">
+        <f>K59+L10</f>
+        <v/>
+      </c>
+      <c r="M59" s="126">
+        <f>L59+M10</f>
+        <v/>
+      </c>
+      <c r="N59" s="126">
+        <f>M59+N10</f>
+        <v/>
+      </c>
+      <c r="O59" s="126">
+        <f>N59+O10</f>
+        <v/>
+      </c>
+      <c r="P59" s="126">
+        <f>O59+P10</f>
+        <v/>
+      </c>
+      <c r="Q59" s="126">
+        <f>P59+Q10</f>
+        <v/>
+      </c>
+      <c r="R59" s="126">
+        <f>Q59+R10</f>
+        <v/>
+      </c>
+      <c r="S59" s="126">
+        <f>R59+S10</f>
+        <v/>
+      </c>
+      <c r="T59" s="126">
+        <f>S59+T10</f>
+        <v/>
+      </c>
+      <c r="U59" s="126">
+        <f>T59+U10</f>
+        <v/>
+      </c>
+      <c r="V59" s="126">
+        <f>U59+V10</f>
+        <v/>
+      </c>
+      <c r="W59" s="126">
+        <f>V59+W10</f>
+        <v/>
+      </c>
+      <c r="X59" s="126">
+        <f>W59+X10</f>
+        <v/>
+      </c>
+      <c r="Y59" s="126">
+        <f>X59+Y10</f>
+        <v/>
+      </c>
       <c r="Z59" s="6" t="n"/>
       <c r="AA59" s="6" t="n"/>
       <c r="AB59" s="6" t="n"/>
     </row>
     <row r="60" ht="19.5" customHeight="1" s="92">
-      <c r="A60" s="128" t="inlineStr">
+      <c r="A60" s="124" t="inlineStr">
         <is>
-          <t>КЛЮЧЕВЫЕ ПОКАЗАТЕЛИ ДЛЯ ИНВЕСТОРА</t>
+          <t>флаг: месяц, в котором заходил транш</t>
         </is>
       </c>
-      <c r="B60" s="128" t="n"/>
-      <c r="C60" s="128" t="n"/>
-      <c r="D60" s="6" t="n"/>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="6" t="n"/>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="6" t="n"/>
-      <c r="I60" s="6" t="n"/>
-      <c r="J60" s="6" t="n"/>
-      <c r="K60" s="6" t="n"/>
-      <c r="L60" s="6" t="n"/>
-      <c r="M60" s="6" t="n"/>
-      <c r="N60" s="6" t="n"/>
-      <c r="O60" s="6" t="n"/>
-      <c r="P60" s="6" t="n"/>
-      <c r="Q60" s="6" t="n"/>
-      <c r="R60" s="6" t="n"/>
-      <c r="S60" s="6" t="n"/>
-      <c r="T60" s="6" t="n"/>
-      <c r="U60" s="6" t="n"/>
-      <c r="V60" s="6" t="n"/>
-      <c r="W60" s="6" t="n"/>
-      <c r="X60" s="6" t="n"/>
-      <c r="Y60" s="6" t="n"/>
+      <c r="B60" s="125">
+        <f>IF(B10&gt;0,B$48,0)</f>
+        <v/>
+      </c>
+      <c r="C60" s="125">
+        <f>IF(C10&gt;0,C$48,0)</f>
+        <v/>
+      </c>
+      <c r="D60" s="125">
+        <f>IF(D10&gt;0,D$48,0)</f>
+        <v/>
+      </c>
+      <c r="E60" s="125">
+        <f>IF(E10&gt;0,E$48,0)</f>
+        <v/>
+      </c>
+      <c r="F60" s="125">
+        <f>IF(F10&gt;0,F$48,0)</f>
+        <v/>
+      </c>
+      <c r="G60" s="125">
+        <f>IF(G10&gt;0,G$48,0)</f>
+        <v/>
+      </c>
+      <c r="H60" s="125">
+        <f>IF(H10&gt;0,H$48,0)</f>
+        <v/>
+      </c>
+      <c r="I60" s="125">
+        <f>IF(I10&gt;0,I$48,0)</f>
+        <v/>
+      </c>
+      <c r="J60" s="125">
+        <f>IF(J10&gt;0,J$48,0)</f>
+        <v/>
+      </c>
+      <c r="K60" s="125">
+        <f>IF(K10&gt;0,K$48,0)</f>
+        <v/>
+      </c>
+      <c r="L60" s="125">
+        <f>IF(L10&gt;0,L$48,0)</f>
+        <v/>
+      </c>
+      <c r="M60" s="125">
+        <f>IF(M10&gt;0,M$48,0)</f>
+        <v/>
+      </c>
+      <c r="N60" s="125">
+        <f>IF(N10&gt;0,N$48,0)</f>
+        <v/>
+      </c>
+      <c r="O60" s="125">
+        <f>IF(O10&gt;0,O$48,0)</f>
+        <v/>
+      </c>
+      <c r="P60" s="125">
+        <f>IF(P10&gt;0,P$48,0)</f>
+        <v/>
+      </c>
+      <c r="Q60" s="125">
+        <f>IF(Q10&gt;0,Q$48,0)</f>
+        <v/>
+      </c>
+      <c r="R60" s="125">
+        <f>IF(R10&gt;0,R$48,0)</f>
+        <v/>
+      </c>
+      <c r="S60" s="125">
+        <f>IF(S10&gt;0,S$48,0)</f>
+        <v/>
+      </c>
+      <c r="T60" s="125">
+        <f>IF(T10&gt;0,T$48,0)</f>
+        <v/>
+      </c>
+      <c r="U60" s="125">
+        <f>IF(U10&gt;0,U$48,0)</f>
+        <v/>
+      </c>
+      <c r="V60" s="125">
+        <f>IF(V10&gt;0,V$48,0)</f>
+        <v/>
+      </c>
+      <c r="W60" s="125">
+        <f>IF(W10&gt;0,W$48,0)</f>
+        <v/>
+      </c>
+      <c r="X60" s="125">
+        <f>IF(X10&gt;0,X$48,0)</f>
+        <v/>
+      </c>
+      <c r="Y60" s="125">
+        <f>IF(Y10&gt;0,Y$48,0)</f>
+        <v/>
+      </c>
       <c r="Z60" s="6" t="n"/>
       <c r="AA60" s="6" t="n"/>
       <c r="AB60" s="6" t="n"/>
     </row>
     <row r="61" ht="19.5" customHeight="1" s="92">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>Пиковая потребность в деньгах (макс. кассовый разрыв)</t>
-        </is>
-      </c>
-      <c r="B61" s="129">
-        <f>MAX(0,-MIN(B54:Y54))</f>
-        <v/>
-      </c>
-      <c r="C61" s="124" t="inlineStr">
-        <is>
-          <t>считается моделью автоматически</t>
-        </is>
-      </c>
+      <c r="A61" s="6" t="n"/>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n"/>
       <c r="D61" s="6" t="n"/>
       <c r="E61" s="6" t="n"/>
       <c r="F61" s="6" t="n"/>
@@ -7415,20 +7551,13 @@
       <c r="AB61" s="6" t="n"/>
     </row>
     <row r="62" ht="19.5" customHeight="1" s="92">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="A62" s="128" t="inlineStr">
         <is>
-          <t>Требуемые инвестиции (с запасом прочности)</t>
+          <t>КЛЮЧЕВЫЕ ПОКАЗАТЕЛИ ДЛЯ ИНВЕСТОРА</t>
         </is>
       </c>
-      <c r="B62" s="129">
-        <f>ROUNDUP(B61*(1+Параметры!$B$62)/100000,0)*100000</f>
-        <v/>
-      </c>
-      <c r="C62" s="124" t="inlineStr">
-        <is>
-          <t>именно эту сумму просим у инвестора</t>
-        </is>
-      </c>
+      <c r="B62" s="128" t="n"/>
+      <c r="C62" s="128" t="n"/>
       <c r="D62" s="6" t="n"/>
       <c r="E62" s="6" t="n"/>
       <c r="F62" s="6" t="n"/>
@@ -7458,14 +7587,18 @@
     <row r="63" ht="19.5" customHeight="1" s="92">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Транш 1 (месяц 1)</t>
+          <t>Первый транш (месяц 1)</t>
         </is>
       </c>
       <c r="B63" s="129">
         <f>B10</f>
         <v/>
       </c>
-      <c r="C63" s="6" t="n"/>
+      <c r="C63" s="124" t="inlineStr">
+        <is>
+          <t>с этой суммы начинаем</t>
+        </is>
+      </c>
       <c r="D63" s="6" t="n"/>
       <c r="E63" s="6" t="n"/>
       <c r="F63" s="6" t="n"/>
@@ -7495,16 +7628,16 @@
     <row r="64" ht="19.5" customHeight="1" s="92">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Транш 2</t>
+          <t>Инвестиции всего за 24 месяца</t>
         </is>
       </c>
       <c r="B64" s="129">
-        <f>$Z$10-B10</f>
+        <f>$Z$10</f>
         <v/>
       </c>
       <c r="C64" s="124" t="inlineStr">
         <is>
-          <t>по достижении KPI</t>
+          <t>сумма всех траншей</t>
         </is>
       </c>
       <c r="D64" s="6" t="n"/>
@@ -7536,11 +7669,11 @@
     <row r="65" ht="19.5" customHeight="1" s="92">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Привлечено инвестиций всего</t>
+          <t>Количество траншей</t>
         </is>
       </c>
-      <c r="B65" s="129">
-        <f>$Z$10</f>
+      <c r="B65" s="130">
+        <f>COUNTIF(B10:Y10,"&gt;0")</f>
         <v/>
       </c>
       <c r="C65" s="6" t="n"/>
@@ -7573,14 +7706,18 @@
     <row r="66" ht="19.5" customHeight="1" s="92">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Обязательство перед инвестором (тело × коэффициент)</t>
+          <t>Максимальный разовый транш</t>
         </is>
       </c>
       <c r="B66" s="129">
-        <f>ROUND($Z$10*Параметры!$B$65,0)</f>
-        <v/>
-      </c>
-      <c r="C66" s="6" t="n"/>
+        <f>MAX(B10:Y10)</f>
+        <v/>
+      </c>
+      <c r="C66" s="124" t="inlineStr">
+        <is>
+          <t>риск инвестора за один раз</t>
+        </is>
+      </c>
       <c r="D66" s="6" t="n"/>
       <c r="E66" s="6" t="n"/>
       <c r="F66" s="6" t="n"/>
@@ -7610,14 +7747,18 @@
     <row r="67" ht="19.5" customHeight="1" s="92">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Возвращено инвестору за 24 месяца</t>
+          <t>Последний месяц привлечения денег</t>
         </is>
       </c>
-      <c r="B67" s="129">
-        <f>$Z$43</f>
-        <v/>
-      </c>
-      <c r="C67" s="6" t="n"/>
+      <c r="B67" s="130">
+        <f>MAX(B60:Y60)</f>
+        <v/>
+      </c>
+      <c r="C67" s="124" t="inlineStr">
+        <is>
+          <t>дальше проект финансирует себя сам</t>
+        </is>
+      </c>
       <c r="D67" s="6" t="n"/>
       <c r="E67" s="6" t="n"/>
       <c r="F67" s="6" t="n"/>
@@ -7647,14 +7788,18 @@
     <row r="68" ht="19.5" customHeight="1" s="92">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Остаток обязательства на конец горизонта</t>
+          <t>Пиковая потребность (макс. просадка опер. потока)</t>
         </is>
       </c>
       <c r="B68" s="129">
-        <f>$AA$43</f>
-        <v/>
-      </c>
-      <c r="C68" s="6" t="n"/>
+        <f>MAX(0,-MIN(B54:Y54))</f>
+        <v/>
+      </c>
+      <c r="C68" s="124" t="inlineStr">
+        <is>
+          <t>суммарный кассовый разрыв проекта</t>
+        </is>
+      </c>
       <c r="D68" s="6" t="n"/>
       <c r="E68" s="6" t="n"/>
       <c r="F68" s="6" t="n"/>
@@ -7684,11 +7829,11 @@
     <row r="69" ht="19.5" customHeight="1" s="92">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>Доход инвестора за 24 месяца</t>
+          <t>Лимит инвестора</t>
         </is>
       </c>
       <c r="B69" s="129">
-        <f>$Z$43-$Z$10</f>
+        <f>Параметры!$B$73</f>
         <v/>
       </c>
       <c r="C69" s="6" t="n"/>
@@ -7721,11 +7866,11 @@
     <row r="70" ht="19.5" customHeight="1" s="92">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>ROI инвестора за 24 месяца</t>
+          <t>Обязательство перед инвестором (тело × коэффициент)</t>
         </is>
       </c>
-      <c r="B70" s="130">
-        <f>IF($Z$10=0,0,($Z$43-$Z$10)/$Z$10)</f>
+      <c r="B70" s="129">
+        <f>ROUND($Z$10*Параметры!$B$71,0)</f>
         <v/>
       </c>
       <c r="C70" s="6" t="n"/>
@@ -7758,18 +7903,14 @@
     <row r="71" ht="19.5" customHeight="1" s="92">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>IRR инвестора, % годовых</t>
+          <t>Возвращено инвестору за 24 месяца</t>
         </is>
       </c>
-      <c r="B71" s="130">
-        <f>IFERROR((1+IRR(B55:Y55))^12-1,"н/д")</f>
-        <v/>
-      </c>
-      <c r="C71" s="124" t="inlineStr">
-        <is>
-          <t>по потоку «транш → возвраты»</t>
-        </is>
-      </c>
+      <c r="B71" s="129">
+        <f>$Z$43</f>
+        <v/>
+      </c>
+      <c r="C71" s="6" t="n"/>
       <c r="D71" s="6" t="n"/>
       <c r="E71" s="6" t="n"/>
       <c r="F71" s="6" t="n"/>
@@ -7799,18 +7940,14 @@
     <row r="72" ht="19.5" customHeight="1" s="92">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>IRR проекта, % годовых</t>
+          <t>Остаток обязательства на конец горизонта</t>
         </is>
       </c>
-      <c r="B72" s="130">
-        <f>IFERROR((1+IRR(B53:Y53))^12-1,"н/д")</f>
-        <v/>
-      </c>
-      <c r="C72" s="124" t="inlineStr">
-        <is>
-          <t>по операционному потоку</t>
-        </is>
-      </c>
+      <c r="B72" s="129">
+        <f>$AA$43</f>
+        <v/>
+      </c>
+      <c r="C72" s="6" t="n"/>
       <c r="D72" s="6" t="n"/>
       <c r="E72" s="6" t="n"/>
       <c r="F72" s="6" t="n"/>
@@ -7840,18 +7977,14 @@
     <row r="73" ht="19.5" customHeight="1" s="92">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>NPV проекта</t>
+          <t>Доход инвестора за 24 месяца</t>
         </is>
       </c>
       <c r="B73" s="129">
-        <f>ROUND(NPV(Параметры!$B$68/12,B53:Y53),0)</f>
-        <v/>
-      </c>
-      <c r="C73" s="124" t="inlineStr">
-        <is>
-          <t>ставка дисконтирования — на листе Параметры</t>
-        </is>
-      </c>
+        <f>$Z$43-$Z$10</f>
+        <v/>
+      </c>
+      <c r="C73" s="6" t="n"/>
       <c r="D73" s="6" t="n"/>
       <c r="E73" s="6" t="n"/>
       <c r="F73" s="6" t="n"/>
@@ -7881,11 +8014,11 @@
     <row r="74" ht="19.5" customHeight="1" s="92">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>Месяц выхода в операционный плюс</t>
+          <t>ROI инвестора за 24 месяца</t>
         </is>
       </c>
       <c r="B74" s="131">
-        <f>IF(MIN(B56:Y56)=9999,"за горизонтом",MIN(B56:Y56))</f>
+        <f>IF($Z$10=0,0,($Z$43-$Z$10)/$Z$10)</f>
         <v/>
       </c>
       <c r="C74" s="6" t="n"/>
@@ -7918,14 +8051,18 @@
     <row r="75" ht="19.5" customHeight="1" s="92">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>Месяц окупаемости проекта (накопленный поток &gt; 0)</t>
+          <t>IRR инвестора, % годовых</t>
         </is>
       </c>
       <c r="B75" s="131">
-        <f>IF(MIN(B57:Y57)=9999,"за горизонтом",MIN(B57:Y57))</f>
-        <v/>
-      </c>
-      <c r="C75" s="6" t="n"/>
+        <f>IFERROR((1+IRR(B55:Y55))^12-1,"н/д")</f>
+        <v/>
+      </c>
+      <c r="C75" s="124" t="inlineStr">
+        <is>
+          <t>по реальному графику траншей и возвратов</t>
+        </is>
+      </c>
       <c r="D75" s="6" t="n"/>
       <c r="E75" s="6" t="n"/>
       <c r="F75" s="6" t="n"/>
@@ -7955,14 +8092,18 @@
     <row r="76" ht="19.5" customHeight="1" s="92">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>Месяц полного возврата инвестору</t>
+          <t>IRR проекта, % годовых</t>
         </is>
       </c>
       <c r="B76" s="131">
-        <f>IF(MIN(B58:Y58)=9999,"за горизонтом",MIN(B58:Y58))</f>
-        <v/>
-      </c>
-      <c r="C76" s="6" t="n"/>
+        <f>IFERROR((1+IRR(B53:Y53))^12-1,"н/д")</f>
+        <v/>
+      </c>
+      <c r="C76" s="124" t="inlineStr">
+        <is>
+          <t>по операционному потоку</t>
+        </is>
+      </c>
       <c r="D76" s="6" t="n"/>
       <c r="E76" s="6" t="n"/>
       <c r="F76" s="6" t="n"/>
@@ -7992,14 +8133,18 @@
     <row r="77" ht="19.5" customHeight="1" s="92">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>Выручка за 24 месяца</t>
+          <t>NPV проекта</t>
         </is>
       </c>
       <c r="B77" s="129">
-        <f>$Z$3+$Z$6+$Z$9</f>
-        <v/>
-      </c>
-      <c r="C77" s="6" t="n"/>
+        <f>ROUND(NPV(Параметры!$B$74/12,B53:Y53),0)</f>
+        <v/>
+      </c>
+      <c r="C77" s="124" t="inlineStr">
+        <is>
+          <t>ставка — на листе «Параметры»</t>
+        </is>
+      </c>
       <c r="D77" s="6" t="n"/>
       <c r="E77" s="6" t="n"/>
       <c r="F77" s="6" t="n"/>
@@ -8029,11 +8174,11 @@
     <row r="78" ht="19.5" customHeight="1" s="92">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>Выручка в 24-м месяце (run-rate)</t>
+          <t>Месяц выхода в операционный плюс</t>
         </is>
       </c>
-      <c r="B78" s="129">
-        <f>$Y$3+$Y$6+$Y$9</f>
+      <c r="B78" s="130">
+        <f>IF(MIN(B56:Y56)=9999,"за горизонтом",MIN(B56:Y56))</f>
         <v/>
       </c>
       <c r="C78" s="6" t="n"/>
@@ -8066,11 +8211,11 @@
     <row r="79" ht="19.5" customHeight="1" s="92">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>Средняя валовая маржа</t>
+          <t>Месяц окупаемости проекта (накопленный поток &gt; 0)</t>
         </is>
       </c>
       <c r="B79" s="130">
-        <f>IF(B77=0,0,($Z$51)/B77)</f>
+        <f>IF(MIN(B57:Y57)=9999,"за горизонтом",MIN(B57:Y57))</f>
         <v/>
       </c>
       <c r="C79" s="6" t="n"/>
@@ -8103,11 +8248,11 @@
     <row r="80" ht="19.5" customHeight="1" s="92">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Операционная прибыль за 24 месяца</t>
+          <t>Месяц полного возврата инвестору</t>
         </is>
       </c>
-      <c r="B80" s="129">
-        <f>$Z$53</f>
+      <c r="B80" s="130">
+        <f>IF(MIN(B58:Y58)=9999,"за горизонтом",MIN(B58:Y58))</f>
         <v/>
       </c>
       <c r="C80" s="6" t="n"/>
@@ -8140,11 +8285,11 @@
     <row r="81" ht="19.5" customHeight="1" s="92">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>Рентабельность по операционному потоку</t>
+          <t>Выручка за 24 месяца</t>
         </is>
       </c>
-      <c r="B81" s="130">
-        <f>IF(B77=0,0,B80/B77)</f>
+      <c r="B81" s="129">
+        <f>$Z$3+$Z$6+$Z$9</f>
         <v/>
       </c>
       <c r="C81" s="6" t="n"/>
@@ -8177,11 +8322,11 @@
     <row r="82" ht="19.5" customHeight="1" s="92">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>Минимальный остаток на счёте за горизонт</t>
+          <t>Выручка в 24-м месяце (run-rate)</t>
         </is>
       </c>
       <c r="B82" s="129">
-        <f>MIN(B46:Y46)</f>
+        <f>$Y$3+$Y$6+$Y$9</f>
         <v/>
       </c>
       <c r="C82" s="6" t="n"/>
@@ -8214,11 +8359,11 @@
     <row r="83" ht="19.5" customHeight="1" s="92">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>Проверка достаточности денег</t>
+          <t>Средняя валовая маржа</t>
         </is>
       </c>
-      <c r="B83" s="132">
-        <f>IF(B82&gt;=0,"ОК: кассовых разрывов нет","ДЕФИЦИТ: поднимите запас прочности")</f>
+      <c r="B83" s="131">
+        <f>IF(B81=0,0,$Z$51/B81)</f>
         <v/>
       </c>
       <c r="C83" s="6" t="n"/>
@@ -8251,18 +8396,14 @@
     <row r="84" ht="19.5" customHeight="1" s="92">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>Оценка компании post-money (по доле инвестора)</t>
+          <t>Операционная прибыль за 24 месяца</t>
         </is>
       </c>
       <c r="B84" s="129">
-        <f>IF(Параметры!$B$69=0,0,ROUND($Z$10/Параметры!$B$69,0))</f>
-        <v/>
-      </c>
-      <c r="C84" s="124" t="inlineStr">
-        <is>
-          <t>альтернатива долговому возврату</t>
-        </is>
-      </c>
+        <f>$Z$53</f>
+        <v/>
+      </c>
+      <c r="C84" s="6" t="n"/>
       <c r="D84" s="6" t="n"/>
       <c r="E84" s="6" t="n"/>
       <c r="F84" s="6" t="n"/>
@@ -8290,8 +8431,15 @@
       <c r="AB84" s="6" t="n"/>
     </row>
     <row r="85" ht="19.5" customHeight="1" s="92">
-      <c r="A85" s="6" t="n"/>
-      <c r="B85" s="6" t="n"/>
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Рентабельность по операционному потоку</t>
+        </is>
+      </c>
+      <c r="B85" s="131">
+        <f>IF(B81=0,0,B84/B81)</f>
+        <v/>
+      </c>
       <c r="C85" s="6" t="n"/>
       <c r="D85" s="6" t="n"/>
       <c r="E85" s="6" t="n"/>
@@ -8320,8 +8468,15 @@
       <c r="AB85" s="6" t="n"/>
     </row>
     <row r="86" ht="19.5" customHeight="1" s="92">
-      <c r="A86" s="6" t="n"/>
-      <c r="B86" s="6" t="n"/>
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Минимальный остаток на счёте за горизонт</t>
+        </is>
+      </c>
+      <c r="B86" s="129">
+        <f>MIN(B46:Y46)</f>
+        <v/>
+      </c>
       <c r="C86" s="6" t="n"/>
       <c r="D86" s="6" t="n"/>
       <c r="E86" s="6" t="n"/>
@@ -8350,8 +8505,15 @@
       <c r="AB86" s="6" t="n"/>
     </row>
     <row r="87" ht="19.5" customHeight="1" s="92">
-      <c r="A87" s="6" t="n"/>
-      <c r="B87" s="6" t="n"/>
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Проверка: денег хватает?</t>
+        </is>
+      </c>
+      <c r="B87" s="132">
+        <f>IF(AND(B86&gt;=0,B64&lt;=B69),"ОК: разрывов нет, уложились в лимит","ДЕФИЦИТ: не хватает лимита инвестора")</f>
+        <v/>
+      </c>
       <c r="C87" s="6" t="n"/>
       <c r="D87" s="6" t="n"/>
       <c r="E87" s="6" t="n"/>
@@ -8380,9 +8542,20 @@
       <c r="AB87" s="6" t="n"/>
     </row>
     <row r="88" ht="19.5" customHeight="1" s="92">
-      <c r="A88" s="6" t="n"/>
-      <c r="B88" s="6" t="n"/>
-      <c r="C88" s="6" t="n"/>
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Оценка компании post-money (по доле инвестора)</t>
+        </is>
+      </c>
+      <c r="B88" s="129">
+        <f>IF(Параметры!$B$75=0,0,ROUND($Z$10/Параметры!$B$75,0))</f>
+        <v/>
+      </c>
+      <c r="C88" s="124" t="inlineStr">
+        <is>
+          <t>альтернатива возврату — доля в капитале</t>
+        </is>
+      </c>
       <c r="D88" s="6" t="n"/>
       <c r="E88" s="6" t="n"/>
       <c r="F88" s="6" t="n"/>
@@ -35721,12 +35894,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" style="92" min="1" max="1"/>
+    <col width="50" customWidth="1" style="92" min="1" max="1"/>
     <col width="15" customWidth="1" style="92" min="2" max="2"/>
-    <col width="40" customWidth="1" style="92" min="3" max="3"/>
+    <col width="42" customWidth="1" style="92" min="3" max="3"/>
     <col width="15" customWidth="1" style="92" min="4" max="4"/>
     <col width="15" customWidth="1" style="92" min="5" max="5"/>
     <col width="15" customWidth="1" style="92" min="6" max="6"/>
@@ -35751,7 +35924,7 @@
     <row r="2">
       <c r="A2" s="134" t="inlineStr">
         <is>
-          <t>Меняйте ТОЛЬКО жёлтые ячейки этого листа — весь ДДС пересчитается сам</t>
+          <t>Меняйте ТОЛЬКО жёлтые ячейки — весь ДДС пересчитается сам</t>
         </is>
       </c>
     </row>
@@ -35793,7 +35966,7 @@
       </c>
       <c r="C5" s="137" t="inlineStr">
         <is>
-          <t>полотно, пошив, печать, бирка, брак</t>
+          <t>полотно, пошив, печать, бирка</t>
         </is>
       </c>
     </row>
@@ -35825,7 +35998,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Товар 3 «B2B командная экипировка» — средний чек заказа</t>
+          <t>Товар 3 «B2B командная экипировка» — чек заказа</t>
         </is>
       </c>
       <c r="B8" s="136" t="n">
@@ -35861,22 +36034,22 @@
       <c r="B11" s="140" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="141" t="inlineStr">
+      <c r="C11" s="139" t="inlineStr">
         <is>
           <t>СЦЕНАРИЙ: 1 — пессимистичный, 2 — базовый, 3 — оптимистичный →</t>
         </is>
       </c>
-      <c r="D11" s="142" t="inlineStr">
+      <c r="D11" s="141" t="inlineStr">
         <is>
           <t>1 — пессимистичный</t>
         </is>
       </c>
-      <c r="E11" s="142" t="inlineStr">
+      <c r="E11" s="141" t="inlineStr">
         <is>
           <t>2 — базовый</t>
         </is>
       </c>
-      <c r="F11" s="142" t="inlineStr">
+      <c r="F11" s="141" t="inlineStr">
         <is>
           <t>3 — оптимистичный</t>
         </is>
@@ -35888,23 +36061,23 @@
           <t>Товар 1 — продажи в 1-й месяц, шт</t>
         </is>
       </c>
-      <c r="B12" s="143">
+      <c r="B12" s="142">
         <f>CHOOSE($B$11,D12,E12,F12)</f>
         <v/>
       </c>
       <c r="C12" s="137" t="inlineStr">
         <is>
-          <t>≈ 20 шт/день на старте</t>
+          <t>стартуем на маркетплейсах, без офиса</t>
         </is>
       </c>
-      <c r="D12" s="144" t="n">
-        <v>520</v>
-      </c>
-      <c r="E12" s="144" t="n">
-        <v>600</v>
-      </c>
-      <c r="F12" s="144" t="n">
-        <v>700</v>
+      <c r="D12" s="143" t="n">
+        <v>270</v>
+      </c>
+      <c r="E12" s="143" t="n">
+        <v>300</v>
+      </c>
+      <c r="F12" s="143" t="n">
+        <v>380</v>
       </c>
     </row>
     <row r="13">
@@ -35913,18 +36086,18 @@
           <t>Товар 1 — рост продаж в месяц, 1-й год</t>
         </is>
       </c>
-      <c r="B13" s="145">
+      <c r="B13" s="144">
         <f>CHOOSE($B$11,D13,E13,F13)</f>
         <v/>
       </c>
       <c r="D13" s="138" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="E13" s="138" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="F13" s="138" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14">
@@ -35933,7 +36106,7 @@
           <t>Товар 1 — рост продаж в месяц, 2-й год</t>
         </is>
       </c>
-      <c r="B14" s="145">
+      <c r="B14" s="144">
         <f>CHOOSE($B$11,D14,E14,F14)</f>
         <v/>
       </c>
@@ -35958,8 +36131,8 @@
           <t>Товар 2 — старт продаж, № месяца</t>
         </is>
       </c>
-      <c r="B15" s="146" t="n">
-        <v>3</v>
+      <c r="B15" s="145" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -35968,18 +36141,18 @@
           <t>Товар 2 — продажи в 1-й месяц запуска, шт</t>
         </is>
       </c>
-      <c r="B16" s="143">
+      <c r="B16" s="142">
         <f>CHOOSE($B$11,D16,E16,F16)</f>
         <v/>
       </c>
-      <c r="D16" s="144" t="n">
-        <v>100</v>
-      </c>
-      <c r="E16" s="144" t="n">
+      <c r="D16" s="143" t="n">
+        <v>80</v>
+      </c>
+      <c r="E16" s="143" t="n">
+        <v>90</v>
+      </c>
+      <c r="F16" s="143" t="n">
         <v>120</v>
-      </c>
-      <c r="F16" s="144" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="17">
@@ -35988,18 +36161,18 @@
           <t>Товар 2 — рост продаж в месяц, 1-й год</t>
         </is>
       </c>
-      <c r="B17" s="145">
+      <c r="B17" s="144">
         <f>CHOOSE($B$11,D17,E17,F17)</f>
         <v/>
       </c>
       <c r="D17" s="138" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="E17" s="138" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F17" s="138" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="18">
@@ -36009,7 +36182,7 @@
         </is>
       </c>
       <c r="B18" s="138" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="19">
@@ -36018,12 +36191,12 @@
           <t>Товар 3 (B2B) — старт продаж, № месяца</t>
         </is>
       </c>
-      <c r="B19" s="146" t="n">
-        <v>5</v>
+      <c r="B19" s="145" t="n">
+        <v>7</v>
       </c>
       <c r="C19" s="137" t="inlineStr">
         <is>
-          <t>после первых отзывов и портфолио</t>
+          <t>после отзывов и портфолио</t>
         </is>
       </c>
     </row>
@@ -36033,17 +36206,17 @@
           <t>Товар 3 (B2B) — заказов в 1-й месяц запуска, шт</t>
         </is>
       </c>
-      <c r="B20" s="143">
+      <c r="B20" s="142">
         <f>CHOOSE($B$11,D20,E20,F20)</f>
         <v/>
       </c>
-      <c r="D20" s="144" t="n">
+      <c r="D20" s="143" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="144" t="n">
+      <c r="E20" s="143" t="n">
         <v>5</v>
       </c>
-      <c r="F20" s="144" t="n">
+      <c r="F20" s="143" t="n">
         <v>7</v>
       </c>
     </row>
@@ -36060,11 +36233,15 @@
     <row r="23">
       <c r="A23" s="135" t="inlineStr">
         <is>
-          <t>3. КОМАНДА — 6 ЧЕЛОВЕК (оклады gross, ₽/мес)</t>
+          <t>3. КОМАНДА — 6 ЧЕЛОВЕК, НАБИРАЕМ ПОСТЕПЕННО</t>
         </is>
       </c>
       <c r="B23" s="135" t="n"/>
-      <c r="C23" s="135" t="n"/>
+      <c r="C23" s="135" t="inlineStr">
+        <is>
+          <t>оклады gross ₽/мес; «месяц выхода» — когда человек появляется в проекте</t>
+        </is>
+      </c>
       <c r="D23" s="135" t="n"/>
       <c r="E23" s="135" t="n"/>
       <c r="F23" s="135" t="n"/>
@@ -36087,595 +36264,689 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2. Менеджер по продажам 1 — оклад</t>
+          <t>1. Руководитель проекта — месяц выхода</t>
         </is>
       </c>
-      <c r="B25" s="136" t="n">
-        <v>45000</v>
+      <c r="B25" s="145" t="n">
+        <v>1</v>
       </c>
       <c r="C25" s="137" t="inlineStr">
         <is>
-          <t>с 1-го месяца</t>
+          <t>основатель, с первого дня</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2. Менеджер по продажам 1 — % от выручки</t>
+          <t>2. Дизайнер принтов и контента — оклад</t>
         </is>
       </c>
-      <c r="B26" s="138" t="n">
-        <v>0.02</v>
+      <c r="B26" s="136" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C26" s="137" t="inlineStr">
+        <is>
+          <t>строка ДДС «Техническая поддержка»</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3. Менеджер по продажам 2 — оклад</t>
+          <t>2. Дизайнер принтов — месяц выхода</t>
         </is>
       </c>
-      <c r="B27" s="136" t="n">
-        <v>45000</v>
+      <c r="B27" s="145" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="137" t="inlineStr">
+        <is>
+          <t>без принтов нет продукта</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3. Менеджер по продажам 2 — % от выручки</t>
+          <t>3. Менеджер по продажам 1 — оклад</t>
         </is>
       </c>
-      <c r="B28" s="138" t="n">
-        <v>0.02</v>
+      <c r="B28" s="136" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3. Менеджер по продажам 2 — выход, № месяца</t>
+          <t>3. Менеджер по продажам 1 — % от выручки</t>
         </is>
       </c>
-      <c r="B29" s="146" t="n">
-        <v>3</v>
-      </c>
-      <c r="C29" s="137" t="inlineStr">
-        <is>
-          <t>нанимаем под запуск товара 2</t>
-        </is>
+      <c r="B29" s="138" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4. Маркетолог — оклад</t>
+          <t>3. Менеджер по продажам 1 — месяц выхода</t>
         </is>
       </c>
-      <c r="B30" s="136" t="n">
-        <v>70000</v>
+      <c r="B30" s="145" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4. Маркетолог — % от выручки</t>
+          <t>4. Маркетолог — оклад</t>
         </is>
       </c>
-      <c r="B31" s="138" t="n">
-        <v>0.01</v>
+      <c r="B31" s="136" t="n">
+        <v>70000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>4. Маркетолог — % от выручки</t>
+        </is>
+      </c>
+      <c r="B32" s="138" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4. Маркетолог — месяц выхода</t>
+        </is>
+      </c>
+      <c r="B33" s="145" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" s="137" t="inlineStr">
+        <is>
+          <t>когда есть что масштабировать</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>5. Разработчик / поддержка сайта — оклад</t>
         </is>
       </c>
-      <c r="B32" s="136" t="n">
+      <c r="B34" s="136" t="n">
         <v>90000</v>
       </c>
-      <c r="C32" s="137" t="inlineStr">
+      <c r="C34" s="137" t="inlineStr">
         <is>
           <t>строка ДДС «Разработка»</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
-          <t>6. Дизайнер принтов и контента — оклад</t>
+          <t>5. Разработчик — месяц выхода</t>
         </is>
       </c>
-      <c r="B33" s="136" t="n">
-        <v>65000</v>
-      </c>
-      <c r="C33" s="137" t="inlineStr">
+      <c r="B35" s="145" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" s="137" t="inlineStr">
         <is>
-          <t>строка ДДС «Техническая поддержка»</t>
+          <t>запуск своего сайта</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>6. Менеджер по продажам 2 (B2B) — оклад</t>
+        </is>
+      </c>
+      <c r="B36" s="136" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>6. Менеджер по продажам 2 — % от выручки</t>
+        </is>
+      </c>
+      <c r="B37" s="138" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>6. Менеджер по продажам 2 — месяц выхода</t>
+        </is>
+      </c>
+      <c r="B38" s="145" t="n">
+        <v>9</v>
+      </c>
+      <c r="C38" s="137" t="inlineStr">
+        <is>
+          <t>под B2B-направление</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Индексация окладов со 2-го года</t>
         </is>
       </c>
-      <c r="B34" s="138" t="n">
+      <c r="B39" s="138" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Страховые взносы, % от ФОТ</t>
         </is>
       </c>
-      <c r="B35" s="138" t="n">
+      <c r="B40" s="138" t="n">
         <v>0.2</v>
       </c>
-      <c r="C35" s="137" t="inlineStr">
+      <c r="C40" s="137" t="inlineStr">
         <is>
           <t>льготный тариф МСП (среднее)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="135" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="135" t="inlineStr">
         <is>
           <t>4. МАРКЕТИНГ</t>
         </is>
       </c>
-      <c r="B37" s="135" t="n"/>
-      <c r="C37" s="135" t="n"/>
-      <c r="D37" s="135" t="n"/>
-      <c r="E37" s="135" t="n"/>
-      <c r="F37" s="135" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="B42" s="135" t="n"/>
+      <c r="C42" s="135" t="n"/>
+      <c r="D42" s="135" t="n"/>
+      <c r="E42" s="135" t="n"/>
+      <c r="F42" s="135" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Реклама интернет, % от выручки</t>
         </is>
       </c>
-      <c r="B38" s="138" t="n">
+      <c r="B43" s="138" t="n">
         <v>0.14</v>
       </c>
-      <c r="C38" s="137" t="inlineStr">
+      <c r="C43" s="137" t="inlineStr">
         <is>
           <t>performance, таргет, блогеры</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Реклама интернет — минимальный бюджет, ₽/мес</t>
         </is>
       </c>
-      <c r="B39" s="136" t="n">
-        <v>350000</v>
-      </c>
-      <c r="C39" s="137" t="inlineStr">
+      <c r="B44" s="136" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C44" s="137" t="inlineStr">
         <is>
-          <t>разгон трафика на старте</t>
+          <t>на старте бюджет небольшой — денег мало</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Реклама оффлайн, ₽/мес</t>
         </is>
       </c>
-      <c r="B40" s="136" t="n">
+      <c r="B45" s="136" t="n">
         <v>80000</v>
       </c>
-      <c r="C40" s="137" t="inlineStr">
+      <c r="C45" s="137" t="inlineStr">
         <is>
           <t>забеги, спортклубы, амбассадоры</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Реклама оффлайн — старт, № месяца</t>
         </is>
       </c>
-      <c r="B41" s="146" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="B46" s="145" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>SEO-продвижение, ₽/мес</t>
         </is>
       </c>
-      <c r="B42" s="136" t="n">
+      <c r="B47" s="136" t="n">
         <v>60000</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>SEO — старт, № месяца</t>
         </is>
       </c>
-      <c r="B43" s="146" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="135" t="inlineStr">
+      <c r="B48" s="145" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="135" t="inlineStr">
         <is>
           <t>5. IT, АДМИНИСТРАТИВНЫЕ И ОПЕРАЦИОННЫЕ РАСХОДЫ</t>
         </is>
       </c>
-      <c r="B45" s="135" t="n"/>
-      <c r="C45" s="135" t="n"/>
-      <c r="D45" s="135" t="n"/>
-      <c r="E45" s="135" t="n"/>
-      <c r="F45" s="135" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="B50" s="135" t="n"/>
+      <c r="C50" s="135" t="n"/>
+      <c r="D50" s="135" t="n"/>
+      <c r="E50" s="135" t="n"/>
+      <c r="F50" s="135" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Хостинг и домен, ₽/мес</t>
         </is>
       </c>
-      <c r="B46" s="136" t="n">
+      <c r="B51" s="136" t="n">
         <v>8000</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Аренда сервера, CRM и сервисы, ₽/мес</t>
         </is>
       </c>
-      <c r="B47" s="136" t="n">
+      <c r="B52" s="136" t="n">
         <v>12000</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Бухобслуживание (аутсорс), ₽/мес</t>
         </is>
       </c>
-      <c r="B48" s="136" t="n">
+      <c r="B53" s="136" t="n">
         <v>25000</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
-          <t>Эквайринг и комиссии маркетплейсов, % от B2C-выручки</t>
+          <t>Эквайринг и комиссии маркетплейсов, % от B2C</t>
         </is>
       </c>
-      <c r="B49" s="138" t="n">
+      <c r="B54" s="138" t="n">
         <v>0.09</v>
       </c>
-      <c r="C49" s="137" t="inlineStr">
+      <c r="C54" s="137" t="inlineStr">
         <is>
           <t>≈ половина продаж через маркетплейсы</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Аренда офиса и мини-склада, ₽/мес</t>
         </is>
       </c>
-      <c r="B50" s="136" t="n">
+      <c r="B55" s="136" t="n">
         <v>90000</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Офис и склад — с какого месяца</t>
+        </is>
+      </c>
+      <c r="B56" s="145" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" s="137" t="inlineStr">
+        <is>
+          <t>до этого удалённо + фулфилмент маркетплейса</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Канцелярия, ПО и прочее, ₽/мес</t>
         </is>
       </c>
-      <c r="B51" s="136" t="n">
+      <c r="B57" s="136" t="n">
         <v>15000</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Связь и интернет, ₽/мес</t>
         </is>
       </c>
-      <c r="B52" s="136" t="n">
+      <c r="B58" s="136" t="n">
         <v>12000</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Логистика и фулфилмент, % от выручки</t>
         </is>
       </c>
-      <c r="B53" s="138" t="n">
+      <c r="B59" s="138" t="n">
         <v>0.06</v>
       </c>
-      <c r="C53" s="137" t="inlineStr">
+      <c r="C59" s="137" t="inlineStr">
         <is>
           <t>часть доставки платит покупатель</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Упаковка, брак и возвраты, % от B2C-выручки</t>
         </is>
       </c>
-      <c r="B54" s="138" t="n">
+      <c r="B60" s="138" t="n">
         <v>0.05</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Первоначальный товарный запас (1 = формируем, 0 = нет)</t>
         </is>
       </c>
-      <c r="B55" s="146" t="n">
+      <c r="B61" s="145" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="137" t="inlineStr">
+      <c r="C61" s="137" t="inlineStr">
         <is>
           <t>в мес. 1 закупаем товар ещё и под продажи мес. 2</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="135" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="135" t="inlineStr">
         <is>
           <t>6. НАЛОГИ</t>
         </is>
       </c>
-      <c r="B57" s="135" t="n"/>
-      <c r="C57" s="135" t="n"/>
-      <c r="D57" s="135" t="n"/>
-      <c r="E57" s="135" t="n"/>
-      <c r="F57" s="135" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="B63" s="135" t="n"/>
+      <c r="C63" s="135" t="n"/>
+      <c r="D63" s="135" t="n"/>
+      <c r="E63" s="135" t="n"/>
+      <c r="F63" s="135" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>УСН «Доходы минус расходы», ставка</t>
         </is>
       </c>
-      <c r="B58" s="138" t="n">
+      <c r="B64" s="138" t="n">
         <v>0.15</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Минимальный налог, % от доходов</t>
         </is>
       </c>
-      <c r="B59" s="138" t="n">
+      <c r="B65" s="138" t="n">
         <v>0.01</v>
       </c>
-      <c r="C59" s="137" t="inlineStr">
+      <c r="C65" s="137" t="inlineStr">
         <is>
           <t>платим, если он больше расчётного</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="135" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="135" t="inlineStr">
         <is>
-          <t>7. УСЛОВИЯ СДЕЛКИ С ИНВЕСТОРОМ</t>
+          <t>7. УСЛОВИЯ СДЕЛКИ: ФИНАНСИРОВАНИЕ ПО ПОТРЕБНОСТИ</t>
         </is>
       </c>
-      <c r="B61" s="135" t="n"/>
-      <c r="C61" s="135" t="n"/>
-      <c r="D61" s="135" t="n"/>
-      <c r="E61" s="135" t="n"/>
-      <c r="F61" s="135" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="B67" s="135" t="n"/>
+      <c r="C67" s="135" t="inlineStr">
         <is>
-          <t>Запас прочности к пиковой потребности</t>
+          <t>деньги заходят траншами по мере необходимости, а не одной суммой</t>
         </is>
       </c>
-      <c r="B62" s="138" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C62" s="137" t="inlineStr">
+      <c r="D67" s="135" t="n"/>
+      <c r="E67" s="135" t="n"/>
+      <c r="F67" s="135" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
-          <t>буфер на отклонение от плана</t>
+          <t>Первый транш (месяц 1), ₽</t>
         </is>
       </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="B68" s="136" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C68" s="137" t="inlineStr">
         <is>
-          <t>Доля 1-го транша (месяц 1)</t>
+          <t>с этого начинаем</t>
         </is>
       </c>
-      <c r="B63" s="138" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
-          <t>2-й транш — № месяца</t>
+          <t>Шаг доливки транша, ₽</t>
         </is>
       </c>
-      <c r="B64" s="146" t="n">
-        <v>6</v>
-      </c>
-      <c r="C64" s="137" t="inlineStr">
+      <c r="B69" s="136" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C69" s="137" t="inlineStr">
         <is>
-          <t>по достижении KPI по выручке</t>
+          <t>кратность последующих траншей</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Целевой остаток на счёте, ₽</t>
+        </is>
+      </c>
+      <c r="B70" s="136" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C70" s="137" t="inlineStr">
+        <is>
+          <t>ниже него не опускаемся — это и есть триггер доливки</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Коэффициент возврата инвестору, ×</t>
         </is>
       </c>
-      <c r="B65" s="147" t="n">
+      <c r="B71" s="146" t="n">
         <v>1.8</v>
       </c>
-      <c r="C65" s="137" t="inlineStr">
+      <c r="C71" s="137" t="inlineStr">
         <is>
-          <t>возвращаем тело + доход: 1,8× вложенного</t>
+          <t>возвращаем тело + доход с каждого транша</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Доля операционного потока на возврат инвестору</t>
         </is>
       </c>
-      <c r="B66" s="138" t="n">
+      <c r="B72" s="138" t="n">
         <v>0.75</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
-          <t>Неснижаемый остаток на счёте (подушка), ₽</t>
+          <t>Лимит инвестора: максимум денег всего, ₽</t>
         </is>
       </c>
-      <c r="B67" s="136" t="n">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="B73" s="136" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="C73" s="137" t="inlineStr">
+        <is>
+          <t>больше этой суммы модель не привлечёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Ставка дисконтирования, % годовых</t>
         </is>
       </c>
-      <c r="B68" s="138" t="n">
+      <c r="B74" s="138" t="n">
         <v>0.25</v>
       </c>
-      <c r="C68" s="137" t="inlineStr">
+      <c r="C74" s="137" t="inlineStr">
         <is>
           <t>для NPV</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Доля инвестора в капитале</t>
         </is>
       </c>
-      <c r="B69" s="138" t="n">
+      <c r="B75" s="138" t="n">
         <v>0.2</v>
       </c>
-      <c r="C69" s="137" t="inlineStr">
+      <c r="C75" s="137" t="inlineStr">
         <is>
           <t>для оценки post-money</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>Сальдо на начало проекта, ₽</t>
         </is>
       </c>
-      <c r="B70" s="136" t="n">
+      <c r="B76" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="C70" s="137" t="inlineStr">
+      <c r="C76" s="137" t="inlineStr">
         <is>
           <t>собственных средств нет</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="135" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="135" t="inlineStr">
         <is>
           <t>8. ЮНИТ-ЭКОНОМИКА (расчёт)</t>
         </is>
       </c>
-      <c r="B72" s="135" t="n"/>
-      <c r="C72" s="135" t="n"/>
-      <c r="D72" s="135" t="n"/>
-      <c r="E72" s="135" t="n"/>
-      <c r="F72" s="135" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="B78" s="135" t="n"/>
+      <c r="C78" s="135" t="n"/>
+      <c r="D78" s="135" t="n"/>
+      <c r="E78" s="135" t="n"/>
+      <c r="F78" s="135" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Маржа с товара 1, ₽</t>
         </is>
       </c>
-      <c r="B73" s="148">
+      <c r="B79" s="147">
         <f>B4-B5</f>
         <v/>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>Маржа с товара 1, %</t>
         </is>
       </c>
-      <c r="B74" s="149">
+      <c r="B80" s="148">
         <f>IF(B4=0,0,(B4-B5)/B4)</f>
         <v/>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Маржа с товара 2, ₽</t>
         </is>
       </c>
-      <c r="B75" s="148">
+      <c r="B81" s="147">
         <f>B6-B7</f>
         <v/>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>Маржа с товара 2, %</t>
         </is>
       </c>
-      <c r="B76" s="149">
+      <c r="B82" s="148">
         <f>IF(B6=0,0,(B6-B7)/B6)</f>
         <v/>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>Маржа с B2B-заказа, ₽</t>
         </is>
       </c>
-      <c r="B77" s="148">
+      <c r="B83" s="147">
         <f>B8*(1-B9)</f>
         <v/>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>Маржа с B2B-заказа, %</t>
         </is>
       </c>
-      <c r="B78" s="149">
+      <c r="B84" s="148">
         <f>1-B9</f>
         <v/>
       </c>
@@ -36691,78 +36962,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" style="92" min="1" max="1"/>
     <col width="18" customWidth="1" style="92" min="2" max="2"/>
-    <col width="84" customWidth="1" style="92" min="3" max="3"/>
+    <col width="82" customWidth="1" style="92" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="92">
-      <c r="A1" s="150" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="149" t="inlineStr">
         <is>
           <t>ПИТЧ ИНВЕСТОРУ — «СПОРТИВНЫЕ ФУТБОЛКИ»</t>
         </is>
       </c>
-      <c r="B1" s="150" t="n"/>
-      <c r="C1" s="150" t="n"/>
-    </row>
-    <row r="2" s="92">
+      <c r="B1" s="149" t="n"/>
+      <c r="C1" s="149" t="n"/>
+    </row>
+    <row r="2">
       <c r="A2" t="inlineStr"/>
     </row>
     <row r="3" ht="30" customHeight="1" s="92">
-      <c r="A3" s="151" t="inlineStr">
+      <c r="A3" s="150" t="inlineStr">
         <is>
           <t>Проблема</t>
         </is>
       </c>
-      <c r="C3" s="152" t="inlineStr">
+      <c r="C3" s="151" t="inlineStr">
         <is>
           <t>Спортивная одежда в РФ после ухода мировых брендов: покупатель хочет качество и быструю кастомизацию, а получает либо дорогой импорт, либо безликий ноунейм.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" s="92">
-      <c r="A4" s="151" t="inlineStr">
+      <c r="A4" s="150" t="inlineStr">
         <is>
           <t>Решение</t>
         </is>
       </c>
-      <c r="C4" s="152" t="inlineStr">
+      <c r="C4" s="151" t="inlineStr">
         <is>
-          <t>D2C-бренд спортивных футболок: собственный сайт + маркетплейсы + печать под заказ. Срок от заказа до отгрузки — 3 дня, кастом-принт от 1 шт.</t>
+          <t>D2C-бренд спортивных футболок: маркетплейсы на старте, дальше собственный сайт и печать под заказ. Срок от заказа до отгрузки — 3 дня, кастом-принт от 1 шт.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="92">
-      <c r="A5" s="151" t="inlineStr">
+      <c r="A5" s="150" t="inlineStr">
         <is>
           <t>Продукт</t>
         </is>
       </c>
-      <c r="C5" s="152" t="inlineStr">
+      <c r="C5" s="151" t="inlineStr">
         <is>
           <t>1) «Базовая» — массовый спрос; 2) «Pro / кастом-принт» — высокая маржа; 3) B2B — экипировка для команд, клубов и корпоративных забегов.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="92">
-      <c r="A6" s="151" t="inlineStr">
+      <c r="A6" s="150" t="inlineStr">
         <is>
           <t>Бизнес-модель</t>
         </is>
       </c>
-      <c r="C6" s="152" t="inlineStr">
+      <c r="C6" s="151" t="inlineStr">
         <is>
-          <t>Контрактное производство (без CAPEX на оборудование) + собственный трафик. Деньги инвестора идут в товарный запас и маркетинг, а не в железо.</t>
+          <t>Контрактное производство, без CAPEX на оборудование. Деньги инвестора идут в товарный запас и трафик — самые быстро оборачиваемые статьи.</t>
         </is>
       </c>
     </row>
-    <row r="7" s="92">
+    <row r="7">
       <c r="A7" t="inlineStr"/>
     </row>
-    <row r="8" s="92">
+    <row r="8">
       <c r="A8" s="135" t="inlineStr">
         <is>
           <t>ЮНИТ-ЭКОНОМИКА</t>
@@ -36771,505 +37042,591 @@
       <c r="B8" s="135" t="n"/>
       <c r="C8" s="135" t="n"/>
     </row>
-    <row r="9" s="92">
+    <row r="9">
       <c r="A9" t="inlineStr">
         <is>
           <t>Средний чек «Базовая»</t>
         </is>
       </c>
-      <c r="B9" s="153">
+      <c r="B9" s="152">
         <f>Параметры!B4</f>
         <v/>
       </c>
       <c r="C9" s="137" t="inlineStr">
         <is>
-          <t>розница, сайт и маркетплейсы</t>
+          <t>розница: сайт и маркетплейсы</t>
         </is>
       </c>
     </row>
-    <row r="10" s="92">
+    <row r="10">
       <c r="A10" t="inlineStr">
         <is>
           <t>Маржа «Базовая»</t>
         </is>
       </c>
-      <c r="B10" s="154">
-        <f>Параметры!B74</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" s="92">
+      <c r="B10" s="153">
+        <f>Параметры!B80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>Маржа «Pro / кастом»</t>
         </is>
       </c>
-      <c r="B11" s="154">
-        <f>Параметры!B76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" s="92">
+      <c r="B11" s="153">
+        <f>Параметры!B82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>Маржа B2B-заказа</t>
         </is>
       </c>
-      <c r="B12" s="154">
-        <f>Параметры!B78</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" s="92">
+      <c r="B12" s="153">
+        <f>Параметры!B84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t>Средняя валовая маржа проекта</t>
         </is>
       </c>
-      <c r="B13" s="154">
-        <f>ДДС!B79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" s="92">
+      <c r="B13" s="153">
+        <f>ДДС!B83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="inlineStr"/>
     </row>
-    <row r="15" s="92">
+    <row r="15">
       <c r="A15" s="135" t="inlineStr">
         <is>
-          <t>КОМАНДА — 6 ЧЕЛОВЕК</t>
+          <t>ЗАПРОС: ДЕНЬГИ ЗАХОДЯТ ТРАНШАМИ, А НЕ ОДНОЙ СУММОЙ</t>
         </is>
       </c>
       <c r="B15" s="135" t="n"/>
       <c r="C15" s="135" t="n"/>
     </row>
-    <row r="16" s="92">
+    <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>Первый транш (месяц 1)</t>
+        </is>
+      </c>
+      <c r="B16" s="152">
+        <f>ДДС!B63</f>
+        <v/>
+      </c>
+      <c r="C16" s="137" t="inlineStr">
+        <is>
+          <t>проверяем спрос на минимальных деньгах</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Инвестиции всего за 24 месяца</t>
+        </is>
+      </c>
+      <c r="B17" s="152">
+        <f>ДДС!B64</f>
+        <v/>
+      </c>
+      <c r="C17" s="137" t="inlineStr">
+        <is>
+          <t>доливаем только по факту потребности</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Количество траншей</t>
+        </is>
+      </c>
+      <c r="B18" s="154">
+        <f>ДДС!B65</f>
+        <v/>
+      </c>
+      <c r="C18" s="137" t="inlineStr">
+        <is>
+          <t>каждый следующий — под достигнутый KPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Максимальный разовый транш</t>
+        </is>
+      </c>
+      <c r="B19" s="152">
+        <f>ДДС!B66</f>
+        <v/>
+      </c>
+      <c r="C19" s="137" t="inlineStr">
+        <is>
+          <t>риск инвестора за один раз</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Последний месяц привлечения</t>
+        </is>
+      </c>
+      <c r="B20" s="154">
+        <f>ДДС!B67</f>
+        <v/>
+      </c>
+      <c r="C20" s="137" t="inlineStr">
+        <is>
+          <t>дальше проект финансирует себя сам</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Лимит инвестора (потолок)</t>
+        </is>
+      </c>
+      <c r="B21" s="152">
+        <f>ДДС!B69</f>
+        <v/>
+      </c>
+      <c r="C21" s="137" t="inlineStr">
+        <is>
+          <t>больше этой суммы не просим</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="135" t="inlineStr">
+        <is>
+          <t>ЧТО ПОЛУЧАЕТ ИНВЕСТОР</t>
+        </is>
+      </c>
+      <c r="B23" s="135" t="n"/>
+      <c r="C23" s="135" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Возврат за 24 мес.</t>
+        </is>
+      </c>
+      <c r="B24" s="152">
+        <f>ДДС!B71</f>
+        <v/>
+      </c>
+      <c r="C24" s="137" t="inlineStr">
+        <is>
+          <t>из операционного потока, не из новых траншей</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Доход инвестора</t>
+        </is>
+      </c>
+      <c r="B25" s="152">
+        <f>ДДС!B73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ROI инвестора за 24 мес.</t>
+        </is>
+      </c>
+      <c r="B26" s="153">
+        <f>ДДС!B74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IRR инвестора, % годовых</t>
+        </is>
+      </c>
+      <c r="B27" s="153">
+        <f>ДДС!B75</f>
+        <v/>
+      </c>
+      <c r="C27" s="137" t="inlineStr">
+        <is>
+          <t>выше, чем при вложении всей суммы сразу</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Месяц полного возврата</t>
+        </is>
+      </c>
+      <c r="B28" s="154">
+        <f>ДДС!B80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Альтернатива: оценка post-money</t>
+        </is>
+      </c>
+      <c r="B29" s="152">
+        <f>ДДС!B88</f>
+        <v/>
+      </c>
+      <c r="C29" s="137" t="inlineStr">
+        <is>
+          <t>при доле инвестора с листа «Параметры»</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>КОМАНДА — 6 ЧЕЛОВЕК, НАБИРАЕМ ПОСТЕПЕННО (цифра = месяц выхода)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>1. Руководитель проекта (CEO)</t>
         </is>
       </c>
-      <c r="B16" s="153">
-        <f>Параметры!B24</f>
-        <v/>
-      </c>
-      <c r="C16" s="137" t="inlineStr">
+      <c r="B32" s="154">
+        <f>Параметры!B25</f>
+        <v/>
+      </c>
+      <c r="C32" s="137" t="inlineStr">
         <is>
           <t>стратегия, продукт, инвестор</t>
         </is>
       </c>
     </row>
-    <row r="17" s="92">
-      <c r="A17" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
-          <t>2. Менеджер по продажам 1</t>
+          <t>2. Дизайнер принтов и контента</t>
         </is>
       </c>
-      <c r="B17" s="153">
-        <f>Параметры!B25</f>
-        <v/>
-      </c>
-      <c r="C17" s="137" t="inlineStr">
+      <c r="B33" s="154">
+        <f>Параметры!B27</f>
+        <v/>
+      </c>
+      <c r="C33" s="137" t="inlineStr">
+        <is>
+          <t>коллекции, визуал, кастом-макеты</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3. Менеджер по продажам 1</t>
+        </is>
+      </c>
+      <c r="B34" s="154">
+        <f>Параметры!B30</f>
+        <v/>
+      </c>
+      <c r="C34" s="137" t="inlineStr">
         <is>
           <t>розница и маркетплейсы, + % от выручки</t>
         </is>
       </c>
     </row>
-    <row r="18" s="92">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3. Менеджер по продажам 2</t>
-        </is>
-      </c>
-      <c r="B18" s="153">
-        <f>Параметры!B27</f>
-        <v/>
-      </c>
-      <c r="C18" s="137" t="inlineStr">
-        <is>
-          <t>B2B-направление, выходит с 4-го месяца</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" s="92">
-      <c r="A19" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>4. Маркетолог</t>
         </is>
       </c>
-      <c r="B19" s="153">
-        <f>Параметры!B30</f>
-        <v/>
-      </c>
-      <c r="C19" s="137" t="inlineStr">
+      <c r="B35" s="154">
+        <f>Параметры!B33</f>
+        <v/>
+      </c>
+      <c r="C35" s="137" t="inlineStr">
         <is>
           <t>трафик, бренд, амбассадоры, + % от выручки</t>
         </is>
       </c>
     </row>
-    <row r="20" s="92">
-      <c r="A20" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>5. Разработчик / поддержка сайта</t>
         </is>
       </c>
-      <c r="B20" s="153">
-        <f>Параметры!B32</f>
-        <v/>
-      </c>
-      <c r="C20" s="137" t="inlineStr">
+      <c r="B36" s="154">
+        <f>Параметры!B35</f>
+        <v/>
+      </c>
+      <c r="C36" s="137" t="inlineStr">
         <is>
-          <t>сайт, интеграции с маркетплейсами</t>
+          <t>свой сайт и интеграции с маркетплейсами</t>
         </is>
       </c>
     </row>
-    <row r="21" s="92">
-      <c r="A21" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
-          <t>6. Дизайнер принтов и контента</t>
+          <t>6. Менеджер по продажам 2 (B2B)</t>
         </is>
       </c>
-      <c r="B21" s="153">
-        <f>Параметры!B33</f>
-        <v/>
-      </c>
-      <c r="C21" s="137" t="inlineStr">
+      <c r="B37" s="154">
+        <f>Параметры!B38</f>
+        <v/>
+      </c>
+      <c r="C37" s="137" t="inlineStr">
         <is>
-          <t>коллекции, визуал, кастом-макеты</t>
+          <t>командная экипировка и опт</t>
         </is>
       </c>
     </row>
-    <row r="22" s="92">
-      <c r="A22" t="inlineStr">
+    <row r="38" ht="30" customHeight="1" s="92">
+      <c r="A38" s="150" t="inlineStr">
         <is>
-          <t>Итого ФОТ первого месяца (с взносами)</t>
+          <t>Почему так</t>
         </is>
       </c>
-      <c r="B22" s="153">
+      <c r="C38" s="151" t="inlineStr">
+        <is>
+          <t>Полный ФОТ на 6 человек проект тянет не с первого месяца, а по мере роста выручки — именно это позволяет стартовать с небольшого транша вместо разовых миллионов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ФОТ 1-го месяца с взносами</t>
+        </is>
+      </c>
+      <c r="B39" s="152">
         <f>ДДС!B34+ДДС!B13+ДДС!B14+ДДС!B19</f>
         <v/>
       </c>
     </row>
-    <row r="23" s="92">
-      <c r="A23" t="inlineStr"/>
-    </row>
-    <row r="24" s="92">
-      <c r="A24" s="135" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
-          <t>ЗАПРОС И УСЛОВИЯ СДЕЛКИ</t>
+          <t>ФОТ 12-го месяца с взносами</t>
         </is>
       </c>
-      <c r="B24" s="135" t="n"/>
-      <c r="C24" s="135" t="n"/>
-    </row>
-    <row r="25" s="92">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Требуемые инвестиции</t>
-        </is>
-      </c>
-      <c r="B25" s="153">
-        <f>ДДС!B62</f>
-        <v/>
-      </c>
-      <c r="C25" s="137" t="inlineStr">
-        <is>
-          <t>двумя траншами, под KPI по выручке</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" s="92">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Транш 1 (месяц 1)</t>
-        </is>
-      </c>
-      <c r="B26" s="153">
-        <f>ДДС!B63</f>
-        <v/>
-      </c>
-      <c r="C26" s="137" t="inlineStr">
-        <is>
-          <t>товарный запас + разгон трафика</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" s="92">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Транш 2</t>
-        </is>
-      </c>
-      <c r="B27" s="153">
-        <f>ДДС!B64</f>
-        <v/>
-      </c>
-      <c r="C27" s="137" t="inlineStr">
-        <is>
-          <t>масштабирование после подтверждения спроса</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" s="92">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Возврат инвестору за 24 мес.</t>
-        </is>
-      </c>
-      <c r="B28" s="153">
-        <f>ДДС!B67</f>
-        <v/>
-      </c>
-      <c r="C28" s="137" t="inlineStr">
-        <is>
-          <t>из операционного потока</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" s="92">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Доход инвестора</t>
-        </is>
-      </c>
-      <c r="B29" s="153">
-        <f>ДДС!B69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" s="92">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ROI инвестора за 24 мес.</t>
-        </is>
-      </c>
-      <c r="B30" s="154">
-        <f>ДДС!B70</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" s="92">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>IRR инвестора, % годовых</t>
-        </is>
-      </c>
-      <c r="B31" s="154">
-        <f>ДДС!B71</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" s="92">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Альтернатива: оценка post-money</t>
-        </is>
-      </c>
-      <c r="B32" s="153">
-        <f>ДДС!B84</f>
-        <v/>
-      </c>
-      <c r="C32" s="137" t="inlineStr">
-        <is>
-          <t>при доле инвестора на листе Параметры</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" s="92">
-      <c r="A33" t="inlineStr"/>
-    </row>
-    <row r="34" s="92">
-      <c r="A34" s="135" t="inlineStr">
+      <c r="B40" s="152">
+        <f>ДДС!M34+ДДС!M13+ДДС!M14+ДДС!M19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="135" t="inlineStr">
         <is>
           <t>ЭКОНОМИКА ПРОЕКТА ЗА 24 МЕСЯЦА</t>
         </is>
       </c>
-      <c r="B34" s="135" t="n"/>
-      <c r="C34" s="135" t="n"/>
-    </row>
-    <row r="35" s="92">
-      <c r="A35" t="inlineStr">
+      <c r="B42" s="135" t="n"/>
+      <c r="C42" s="135" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Сценарий модели (1 песс. / 2 базовый / 3 опт.)</t>
         </is>
       </c>
-      <c r="B35" s="155">
+      <c r="B43" s="154">
         <f>Параметры!B11</f>
         <v/>
       </c>
-      <c r="C35" s="137" t="inlineStr">
+      <c r="C43" s="137" t="inlineStr">
         <is>
           <t>переключается одной ячейкой на листе «Параметры»</t>
         </is>
       </c>
     </row>
-    <row r="36" s="92">
-      <c r="A36" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Выручка за 24 месяца</t>
         </is>
       </c>
-      <c r="B36" s="153">
-        <f>ДДС!B77</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" s="92">
-      <c r="A37" t="inlineStr">
+      <c r="B44" s="152">
+        <f>ДДС!B81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Выручка в 24-м месяце (run-rate)</t>
         </is>
       </c>
-      <c r="B37" s="153">
-        <f>ДДС!B78</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" s="92">
-      <c r="A38" t="inlineStr">
+      <c r="B45" s="152">
+        <f>ДДС!B82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Операционная прибыль за 24 месяца</t>
         </is>
       </c>
-      <c r="B38" s="153">
-        <f>ДДС!B80</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" s="92">
-      <c r="A39" t="inlineStr">
+      <c r="B46" s="152">
+        <f>ДДС!B84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Рентабельность по операционному потоку</t>
         </is>
       </c>
-      <c r="B39" s="154">
-        <f>ДДС!B81</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" s="92">
-      <c r="A40" t="inlineStr">
+      <c r="B47" s="153">
+        <f>ДДС!B85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>NPV проекта (ставка 25% годовых)</t>
         </is>
       </c>
-      <c r="B40" s="153">
-        <f>ДДС!B73</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" s="92">
-      <c r="A41" t="inlineStr">
+      <c r="B48" s="152">
+        <f>ДДС!B77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Месяц выхода в операционный плюс</t>
         </is>
       </c>
-      <c r="B41" s="155">
-        <f>ДДС!B74</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" s="92">
-      <c r="A42" t="inlineStr">
+      <c r="B49" s="154">
+        <f>ДДС!B78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Месяц окупаемости проекта</t>
         </is>
       </c>
-      <c r="B42" s="155">
-        <f>ДДС!B75</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" s="92">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Месяц полного возврата инвестору</t>
-        </is>
-      </c>
-      <c r="B43" s="155">
-        <f>ДДС!B76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" s="92">
-      <c r="A44" t="inlineStr">
+      <c r="B50" s="154">
+        <f>ДДС!B79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Минимальный остаток на счёте</t>
         </is>
       </c>
-      <c r="B44" s="153">
-        <f>ДДС!B82</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" s="92">
-      <c r="A45" t="inlineStr">
+      <c r="B51" s="152">
+        <f>ДДС!B86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Проверка достаточности денег</t>
         </is>
       </c>
-      <c r="B45" s="155">
-        <f>ДДС!B83</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" s="92">
-      <c r="A46" t="inlineStr"/>
-    </row>
-    <row r="47" s="92">
-      <c r="A47" s="135" t="inlineStr">
+      <c r="B52" s="154">
+        <f>ДДС!B87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="135" t="inlineStr">
         <is>
           <t>РИСКИ И ОТВЕТ НА НИХ</t>
         </is>
       </c>
-      <c r="B47" s="135" t="n"/>
-      <c r="C47" s="135" t="n"/>
-    </row>
-    <row r="48" ht="30" customHeight="1" s="92">
-      <c r="A48" s="151" t="inlineStr">
+      <c r="B54" s="135" t="n"/>
+      <c r="C54" s="135" t="n"/>
+    </row>
+    <row r="55" ht="30" customHeight="1" s="92">
+      <c r="A55" s="150" t="inlineStr">
         <is>
           <t>Спрос ниже плана</t>
         </is>
       </c>
-      <c r="C48" s="152" t="inlineStr">
+      <c r="C55" s="151" t="inlineStr">
         <is>
-          <t>Модель на формулах: снижаем рост продаж на листе «Параметры» и сразу видим новую потребность в деньгах. Реклама привязана к % от выручки — бюджет не «горит».</t>
+          <t>Риск инвестора ограничен размером транша: если гипотеза не подтвердилась — следующий транш просто не выдаётся. Сценарий переключается одной ячейкой.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1" s="92">
-      <c r="A49" s="151" t="inlineStr">
+    <row r="56" ht="30" customHeight="1" s="92">
+      <c r="A56" s="150" t="inlineStr">
         <is>
           <t>Рост себестоимости / курс</t>
         </is>
       </c>
-      <c r="C49" s="152" t="inlineStr">
+      <c r="C56" s="151" t="inlineStr">
         <is>
           <t>Контрактное производство в РФ, два поставщика, себестоимость — параметр модели.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1" s="92">
-      <c r="A50" s="151" t="inlineStr">
+    <row r="57" ht="30" customHeight="1" s="92">
+      <c r="A57" s="150" t="inlineStr">
         <is>
           <t>Кассовый разрыв</t>
         </is>
       </c>
-      <c r="C50" s="152" t="inlineStr">
+      <c r="C57" s="151" t="inlineStr">
         <is>
-          <t>Неснижаемый остаток на счёте и возврат инвестору только из операционного потока.</t>
+          <t>Модель сама считает месяц и размер доливки; возврат инвестору идёт только из операционного потока и не может увести остаток ниже целевого.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1" s="92">
-      <c r="A51" s="151" t="inlineStr">
+    <row r="58" ht="30" customHeight="1" s="92">
+      <c r="A58" s="150" t="inlineStr">
         <is>
           <t>Уход ключевого человека</t>
         </is>
       </c>
-      <c r="C51" s="152" t="inlineStr">
+      <c r="C58" s="151" t="inlineStr">
         <is>
-          <t>Команда 6 человек, у продавцов и маркетолога % от выручки — доход привязан к результату.</t>
+          <t>У продающих ролей доход привязан к выручке; на старте команда минимальная, новые люди выходят только под подтверждённый рост.</t>
         </is>
       </c>
     </row>
